--- a/output/yearly_population_iteration_93_growth_param_0.5.xlsx
+++ b/output/yearly_population_iteration_93_growth_param_0.5.xlsx
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5049</v>
+        <v>5689</v>
       </c>
       <c r="C2" t="n">
-        <v>11105</v>
+        <v>6040</v>
       </c>
       <c r="D2" t="n">
-        <v>20982</v>
+        <v>37056</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3126</v>
+        <v>3821</v>
       </c>
       <c r="C3" t="n">
-        <v>5387</v>
+        <v>4443</v>
       </c>
       <c r="D3" t="n">
-        <v>16424</v>
+        <v>15154</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2561</v>
+        <v>2887</v>
       </c>
       <c r="C4" t="n">
-        <v>5630</v>
+        <v>5401</v>
       </c>
       <c r="D4" t="n">
-        <v>7791</v>
+        <v>7273</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1744</v>
+        <v>1834</v>
       </c>
       <c r="C5" t="n">
-        <v>4349</v>
+        <v>3949</v>
       </c>
       <c r="D5" t="n">
-        <v>2852</v>
+        <v>2632</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>978</v>
+        <v>1044</v>
       </c>
       <c r="C6" t="n">
-        <v>2695</v>
+        <v>2318</v>
       </c>
       <c r="D6" t="n">
-        <v>1153</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>445</v>
+        <v>466</v>
       </c>
       <c r="C7" t="n">
-        <v>1687</v>
+        <v>1348</v>
       </c>
       <c r="D7" t="n">
-        <v>653</v>
+        <v>650</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="C8" t="n">
-        <v>889</v>
+        <v>679</v>
       </c>
       <c r="D8" t="n">
-        <v>433</v>
+        <v>440</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C9" t="n">
-        <v>392</v>
+        <v>327</v>
       </c>
       <c r="D9" t="n">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="10">
@@ -895,10 +895,10 @@
         <v>39</v>
       </c>
       <c r="C10" t="n">
-        <v>220</v>
+        <v>212</v>
       </c>
       <c r="D10" t="n">
-        <v>244</v>
+        <v>247</v>
       </c>
     </row>
     <row r="11">
@@ -909,10 +909,10 @@
         <v>26</v>
       </c>
       <c r="C11" t="n">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="D11" t="n">
-        <v>206</v>
+        <v>204</v>
       </c>
     </row>
     <row r="12">
@@ -923,10 +923,10 @@
         <v>17</v>
       </c>
       <c r="C12" t="n">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="D12" t="n">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="13">
@@ -937,10 +937,10 @@
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="D13" t="n">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
     <row r="14">
@@ -951,10 +951,10 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="D14" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="15">
@@ -968,7 +968,7 @@
         <v>60</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>82</v>
       </c>
     </row>
     <row r="16">
@@ -982,7 +982,7 @@
         <v>47</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="17">
@@ -993,10 +993,10 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="18">
@@ -1007,7 +1007,7 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D18" t="n">
         <v>39</v>
@@ -1024,7 +1024,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="20">
@@ -1038,7 +1038,7 @@
         <v>29</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="21">
@@ -1049,7 +1049,7 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D21" t="n">
         <v>9</v>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7590</v>
+        <v>6771</v>
       </c>
       <c r="C2" t="n">
-        <v>12877</v>
+        <v>7834</v>
       </c>
       <c r="D2" t="n">
-        <v>17703</v>
+        <v>30830</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3241</v>
+        <v>3812</v>
       </c>
       <c r="C3" t="n">
-        <v>7027</v>
+        <v>4554</v>
       </c>
       <c r="D3" t="n">
-        <v>15940</v>
+        <v>17114</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2427</v>
+        <v>2851</v>
       </c>
       <c r="C4" t="n">
-        <v>5342</v>
+        <v>4767</v>
       </c>
       <c r="D4" t="n">
-        <v>8963</v>
+        <v>8268</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1855</v>
+        <v>2025</v>
       </c>
       <c r="C5" t="n">
-        <v>4861</v>
+        <v>4563</v>
       </c>
       <c r="D5" t="n">
-        <v>3496</v>
+        <v>3309</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1188</v>
+        <v>1266</v>
       </c>
       <c r="C6" t="n">
-        <v>3388</v>
+        <v>3023</v>
       </c>
       <c r="D6" t="n">
-        <v>1398</v>
+        <v>1318</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>606</v>
+        <v>647</v>
       </c>
       <c r="C7" t="n">
-        <v>2140</v>
+        <v>1794</v>
       </c>
       <c r="D7" t="n">
-        <v>713</v>
+        <v>715</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>250</v>
+        <v>262</v>
       </c>
       <c r="C8" t="n">
-        <v>1224</v>
+        <v>967</v>
       </c>
       <c r="D8" t="n">
-        <v>460</v>
+        <v>462</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="C9" t="n">
-        <v>601</v>
+        <v>478</v>
       </c>
       <c r="D9" t="n">
-        <v>320</v>
+        <v>326</v>
       </c>
     </row>
     <row r="10">
@@ -1203,10 +1203,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C10" t="n">
-        <v>286</v>
+        <v>257</v>
       </c>
       <c r="D10" t="n">
         <v>250</v>
@@ -1220,10 +1220,10 @@
         <v>28</v>
       </c>
       <c r="C11" t="n">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="D11" t="n">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="12">
@@ -1234,10 +1234,10 @@
         <v>18</v>
       </c>
       <c r="C12" t="n">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="D12" t="n">
-        <v>164</v>
+        <v>161</v>
       </c>
     </row>
     <row r="13">
@@ -1245,13 +1245,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="D13" t="n">
-        <v>124</v>
+        <v>128</v>
       </c>
     </row>
     <row r="14">
@@ -1262,10 +1262,10 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="D14" t="n">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="15">
@@ -1276,10 +1276,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>83</v>
       </c>
     </row>
     <row r="16">
@@ -1290,10 +1290,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="17">
@@ -1307,7 +1307,7 @@
         <v>40</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="18">
@@ -1318,7 +1318,7 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D18" t="n">
         <v>39</v>
@@ -1335,7 +1335,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="20">
@@ -1349,7 +1349,7 @@
         <v>29</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="21">
@@ -1360,7 +1360,7 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="D21" t="n">
         <v>10</v>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8043</v>
+        <v>7947</v>
       </c>
       <c r="C2" t="n">
-        <v>10017</v>
+        <v>8012</v>
       </c>
       <c r="D2" t="n">
-        <v>20702</v>
+        <v>35179</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4019</v>
+        <v>4093</v>
       </c>
       <c r="C3" t="n">
-        <v>8381</v>
+        <v>5262</v>
       </c>
       <c r="D3" t="n">
-        <v>15120</v>
+        <v>17746</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2352</v>
+        <v>2772</v>
       </c>
       <c r="C4" t="n">
-        <v>5974</v>
+        <v>4525</v>
       </c>
       <c r="D4" t="n">
-        <v>9762</v>
+        <v>9296</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1862</v>
+        <v>2101</v>
       </c>
       <c r="C5" t="n">
-        <v>4916</v>
+        <v>4558</v>
       </c>
       <c r="D5" t="n">
-        <v>4143</v>
+        <v>3970</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1341</v>
+        <v>1440</v>
       </c>
       <c r="C6" t="n">
-        <v>3932</v>
+        <v>3616</v>
       </c>
       <c r="D6" t="n">
-        <v>1681</v>
+        <v>1574</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>748</v>
+        <v>815</v>
       </c>
       <c r="C7" t="n">
-        <v>2652</v>
+        <v>2311</v>
       </c>
       <c r="D7" t="n">
-        <v>792</v>
+        <v>796</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>341</v>
+        <v>365</v>
       </c>
       <c r="C8" t="n">
-        <v>1570</v>
+        <v>1289</v>
       </c>
       <c r="D8" t="n">
-        <v>490</v>
+        <v>487</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>134</v>
+        <v>141</v>
       </c>
       <c r="C9" t="n">
-        <v>832</v>
+        <v>664</v>
       </c>
       <c r="D9" t="n">
-        <v>331</v>
+        <v>341</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C10" t="n">
-        <v>403</v>
+        <v>341</v>
       </c>
       <c r="D10" t="n">
-        <v>256</v>
+        <v>254</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C11" t="n">
-        <v>220</v>
+        <v>209</v>
       </c>
       <c r="D11" t="n">
-        <v>207</v>
+        <v>210</v>
       </c>
     </row>
     <row r="12">
@@ -1545,10 +1545,10 @@
         <v>19</v>
       </c>
       <c r="C12" t="n">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="D12" t="n">
-        <v>167</v>
+        <v>163</v>
       </c>
     </row>
     <row r="13">
@@ -1559,10 +1559,10 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="D13" t="n">
-        <v>125</v>
+        <v>130</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C14" t="n">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="D14" t="n">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="15">
@@ -1587,10 +1587,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>83</v>
       </c>
     </row>
     <row r="16">
@@ -1601,10 +1601,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="17">
@@ -1615,10 +1615,10 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="18">
@@ -1643,10 +1643,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="20">
@@ -1660,7 +1660,7 @@
         <v>29</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="21">
@@ -1671,7 +1671,7 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="D21" t="n">
         <v>11</v>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7298</v>
+        <v>7204</v>
       </c>
       <c r="C2" t="n">
-        <v>6811</v>
+        <v>5384</v>
       </c>
       <c r="D2" t="n">
-        <v>17142</v>
+        <v>28543</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4572</v>
+        <v>5012</v>
       </c>
       <c r="C3" t="n">
-        <v>11656</v>
+        <v>7858</v>
       </c>
       <c r="D3" t="n">
-        <v>16933</v>
+        <v>19402</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1720</v>
+        <v>1941</v>
       </c>
       <c r="C4" t="n">
-        <v>8045</v>
+        <v>6938</v>
       </c>
       <c r="D4" t="n">
-        <v>9236</v>
+        <v>8863</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1239</v>
+        <v>1330</v>
       </c>
       <c r="C5" t="n">
-        <v>3853</v>
+        <v>3543</v>
       </c>
       <c r="D5" t="n">
-        <v>2761</v>
+        <v>2647</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>691</v>
+        <v>753</v>
       </c>
       <c r="C6" t="n">
-        <v>2598</v>
+        <v>2264</v>
       </c>
       <c r="D6" t="n">
-        <v>776</v>
+        <v>780</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>315</v>
+        <v>337</v>
       </c>
       <c r="C7" t="n">
-        <v>1538</v>
+        <v>1263</v>
       </c>
       <c r="D7" t="n">
-        <v>480</v>
+        <v>477</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>123</v>
+        <v>130</v>
       </c>
       <c r="C8" t="n">
-        <v>815</v>
+        <v>650</v>
       </c>
       <c r="D8" t="n">
-        <v>324</v>
+        <v>334</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C9" t="n">
-        <v>394</v>
+        <v>334</v>
       </c>
       <c r="D9" t="n">
-        <v>250</v>
+        <v>248</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C10" t="n">
-        <v>215</v>
+        <v>204</v>
       </c>
       <c r="D10" t="n">
-        <v>202</v>
+        <v>205</v>
       </c>
     </row>
     <row r="11">
@@ -1842,10 +1842,10 @@
         <v>17</v>
       </c>
       <c r="C11" t="n">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="D11" t="n">
-        <v>163</v>
+        <v>159</v>
       </c>
     </row>
     <row r="12">
@@ -1856,10 +1856,10 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="D12" t="n">
-        <v>122</v>
+        <v>127</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C13" t="n">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="D13" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="14">
@@ -1884,10 +1884,10 @@
         <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="D14" t="n">
-        <v>77</v>
+        <v>81</v>
       </c>
     </row>
     <row r="15">
@@ -1898,10 +1898,10 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D15" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
     <row r="16">
@@ -1912,10 +1912,10 @@
         <v>1</v>
       </c>
       <c r="C16" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D16" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="17">
@@ -1940,10 +1940,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D18" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="19">
@@ -1957,7 +1957,7 @@
         <v>28</v>
       </c>
       <c r="D19" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="20">
@@ -1968,7 +1968,7 @@
         <v>8</v>
       </c>
       <c r="C20" t="n">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="D20" t="n">
         <v>11</v>
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4292</v>
+        <v>4360</v>
       </c>
       <c r="C2" t="n">
-        <v>3185</v>
+        <v>2557</v>
       </c>
       <c r="D2" t="n">
-        <v>12031</v>
+        <v>19972</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4906</v>
+        <v>5138</v>
       </c>
       <c r="C3" t="n">
-        <v>8540</v>
+        <v>6054</v>
       </c>
       <c r="D3" t="n">
-        <v>15986</v>
+        <v>19755</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2423</v>
+        <v>2718</v>
       </c>
       <c r="C4" t="n">
-        <v>9885</v>
+        <v>7501</v>
       </c>
       <c r="D4" t="n">
-        <v>10314</v>
+        <v>10382</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1350</v>
+        <v>1486</v>
       </c>
       <c r="C5" t="n">
-        <v>5688</v>
+        <v>5073</v>
       </c>
       <c r="D5" t="n">
-        <v>3538</v>
+        <v>3393</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>830</v>
+        <v>898</v>
       </c>
       <c r="C6" t="n">
-        <v>3164</v>
+        <v>2833</v>
       </c>
       <c r="D6" t="n">
-        <v>979</v>
+        <v>972</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>297</v>
+        <v>319</v>
       </c>
       <c r="C7" t="n">
-        <v>1963</v>
+        <v>1658</v>
       </c>
       <c r="D7" t="n">
-        <v>524</v>
+        <v>521</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>103</v>
+        <v>110</v>
       </c>
       <c r="C8" t="n">
-        <v>1050</v>
+        <v>847</v>
       </c>
       <c r="D8" t="n">
-        <v>338</v>
+        <v>345</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C9" t="n">
-        <v>450</v>
+        <v>393</v>
       </c>
       <c r="D9" t="n">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="10">
@@ -2139,10 +2139,10 @@
         <v>15</v>
       </c>
       <c r="C10" t="n">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="D10" t="n">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="11">
@@ -2153,7 +2153,7 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="D11" t="n">
         <v>166</v>
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C12" t="n">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="D12" t="n">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="13">
@@ -2181,10 +2181,10 @@
         <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="D13" t="n">
-        <v>96</v>
+        <v>101</v>
       </c>
     </row>
     <row r="14">
@@ -2195,10 +2195,10 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D14" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="15">
@@ -2209,10 +2209,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D15" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="16">
@@ -2237,10 +2237,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D17" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="18">
@@ -2254,7 +2254,7 @@
         <v>27</v>
       </c>
       <c r="D18" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="19">
@@ -2265,7 +2265,7 @@
         <v>7</v>
       </c>
       <c r="C19" t="n">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="D19" t="n">
         <v>10</v>
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4645</v>
+        <v>6185</v>
       </c>
       <c r="C2" t="n">
-        <v>7826</v>
+        <v>8305</v>
       </c>
       <c r="D2" t="n">
-        <v>15442</v>
+        <v>17234</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3942</v>
+        <v>4029</v>
       </c>
       <c r="C3" t="n">
-        <v>5342</v>
+        <v>3815</v>
       </c>
       <c r="D3" t="n">
-        <v>14470</v>
+        <v>18427</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2973</v>
+        <v>3271</v>
       </c>
       <c r="C4" t="n">
-        <v>9020</v>
+        <v>6680</v>
       </c>
       <c r="D4" t="n">
-        <v>10926</v>
+        <v>11686</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1603</v>
+        <v>1791</v>
       </c>
       <c r="C5" t="n">
-        <v>7543</v>
+        <v>6132</v>
       </c>
       <c r="D5" t="n">
-        <v>4471</v>
+        <v>4430</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>962</v>
+        <v>1055</v>
       </c>
       <c r="C6" t="n">
-        <v>4302</v>
+        <v>3864</v>
       </c>
       <c r="D6" t="n">
-        <v>1334</v>
+        <v>1330</v>
       </c>
     </row>
     <row r="7">
@@ -2405,10 +2405,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>447</v>
+        <v>488</v>
       </c>
       <c r="C7" t="n">
-        <v>2499</v>
+        <v>2175</v>
       </c>
       <c r="D7" t="n">
         <v>581</v>
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>150</v>
+        <v>163</v>
       </c>
       <c r="C8" t="n">
-        <v>1426</v>
+        <v>1196</v>
       </c>
       <c r="D8" t="n">
-        <v>358</v>
+        <v>369</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="C9" t="n">
-        <v>677</v>
+        <v>578</v>
       </c>
       <c r="D9" t="n">
-        <v>265</v>
+        <v>267</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C10" t="n">
-        <v>311</v>
+        <v>289</v>
       </c>
       <c r="D10" t="n">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="11">
@@ -2464,7 +2464,7 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="D11" t="n">
         <v>169</v>
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C12" t="n">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="D12" t="n">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="13">
@@ -2492,10 +2492,10 @@
         <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="D13" t="n">
-        <v>99</v>
+        <v>102</v>
       </c>
     </row>
     <row r="14">
@@ -2506,10 +2506,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D14" t="n">
-        <v>62</v>
+        <v>66</v>
       </c>
     </row>
     <row r="15">
@@ -2520,7 +2520,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D15" t="n">
         <v>48</v>
@@ -2548,10 +2548,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D17" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="18">
@@ -2562,10 +2562,10 @@
         <v>6</v>
       </c>
       <c r="C18" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="D18" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="19">
@@ -2576,7 +2576,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D19" t="n">
         <v>7</v>
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2740</v>
+        <v>3602</v>
       </c>
       <c r="C2" t="n">
-        <v>3673</v>
+        <v>3741</v>
       </c>
       <c r="D2" t="n">
-        <v>10776</v>
+        <v>11923</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3966</v>
+        <v>4402</v>
       </c>
       <c r="C3" t="n">
-        <v>6014</v>
+        <v>5267</v>
       </c>
       <c r="D3" t="n">
-        <v>14246</v>
+        <v>17851</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3299</v>
+        <v>3616</v>
       </c>
       <c r="C4" t="n">
-        <v>8497</v>
+        <v>6256</v>
       </c>
       <c r="D4" t="n">
-        <v>11467</v>
+        <v>12538</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1682</v>
+        <v>1876</v>
       </c>
       <c r="C5" t="n">
-        <v>9037</v>
+        <v>7101</v>
       </c>
       <c r="D5" t="n">
-        <v>4707</v>
+        <v>4831</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>804</v>
+        <v>889</v>
       </c>
       <c r="C6" t="n">
-        <v>5108</v>
+        <v>4708</v>
       </c>
       <c r="D6" t="n">
-        <v>1305</v>
+        <v>1309</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>138</v>
+        <v>150</v>
       </c>
       <c r="C7" t="n">
-        <v>2629</v>
+        <v>2256</v>
       </c>
       <c r="D7" t="n">
-        <v>581</v>
+        <v>588</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="C8" t="n">
-        <v>1096</v>
+        <v>953</v>
       </c>
       <c r="D8" t="n">
-        <v>378</v>
+        <v>386</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C9" t="n">
-        <v>304</v>
+        <v>283</v>
       </c>
       <c r="D9" t="n">
-        <v>289</v>
+        <v>293</v>
       </c>
     </row>
     <row r="10">
@@ -2761,7 +2761,7 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="D10" t="n">
         <v>165</v>
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C11" t="n">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="D11" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="D12" t="n">
-        <v>97</v>
+        <v>99</v>
       </c>
     </row>
     <row r="13">
@@ -2803,10 +2803,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D13" t="n">
-        <v>60</v>
+        <v>64</v>
       </c>
     </row>
     <row r="14">
@@ -2817,7 +2817,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D14" t="n">
         <v>47</v>
@@ -2845,10 +2845,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D16" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="17">
@@ -2859,10 +2859,10 @@
         <v>5</v>
       </c>
       <c r="C17" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D17" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="18">
@@ -2873,7 +2873,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D18" t="n">
         <v>6</v>
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2859</v>
+        <v>3944</v>
       </c>
       <c r="C2" t="n">
-        <v>7671</v>
+        <v>4399</v>
       </c>
       <c r="D2" t="n">
-        <v>9317</v>
+        <v>11483</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2959</v>
+        <v>3460</v>
       </c>
       <c r="C3" t="n">
-        <v>4413</v>
+        <v>4054</v>
       </c>
       <c r="D3" t="n">
-        <v>12953</v>
+        <v>15845</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3116</v>
+        <v>3441</v>
       </c>
       <c r="C4" t="n">
-        <v>7152</v>
+        <v>5651</v>
       </c>
       <c r="D4" t="n">
-        <v>11545</v>
+        <v>13023</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2068</v>
+        <v>2301</v>
       </c>
       <c r="C5" t="n">
-        <v>8692</v>
+        <v>6632</v>
       </c>
       <c r="D5" t="n">
-        <v>5537</v>
+        <v>5867</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1039</v>
+        <v>1163</v>
       </c>
       <c r="C6" t="n">
-        <v>6820</v>
+        <v>5743</v>
       </c>
       <c r="D6" t="n">
-        <v>1745</v>
+        <v>1811</v>
       </c>
     </row>
     <row r="7">
@@ -3027,10 +3027,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>301</v>
+        <v>338</v>
       </c>
       <c r="C7" t="n">
-        <v>3625</v>
+        <v>3308</v>
       </c>
       <c r="D7" t="n">
         <v>673</v>
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="C8" t="n">
-        <v>1672</v>
+        <v>1456</v>
       </c>
       <c r="D8" t="n">
-        <v>399</v>
+        <v>409</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C9" t="n">
-        <v>568</v>
+        <v>514</v>
       </c>
       <c r="D9" t="n">
-        <v>296</v>
+        <v>304</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C10" t="n">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="D10" t="n">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C11" t="n">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="D11" t="n">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="D12" t="n">
-        <v>98</v>
+        <v>101</v>
       </c>
     </row>
     <row r="13">
@@ -3114,10 +3114,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="D13" t="n">
-        <v>60</v>
+        <v>64</v>
       </c>
     </row>
     <row r="14">
@@ -3128,7 +3128,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D14" t="n">
         <v>47</v>
@@ -3145,7 +3145,7 @@
         <v>38</v>
       </c>
       <c r="D15" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="16">
@@ -3156,10 +3156,10 @@
         <v>4</v>
       </c>
       <c r="C16" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D16" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="17">
@@ -3170,7 +3170,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="D17" t="n">
         <v>10</v>
@@ -3184,7 +3184,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D18" t="n">
         <v>2</v>
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2066</v>
+        <v>2755</v>
       </c>
       <c r="C2" t="n">
-        <v>5310</v>
+        <v>2699</v>
       </c>
       <c r="D2" t="n">
-        <v>8657</v>
+        <v>8881</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2565</v>
+        <v>3169</v>
       </c>
       <c r="C3" t="n">
-        <v>5157</v>
+        <v>3837</v>
       </c>
       <c r="D3" t="n">
-        <v>11812</v>
+        <v>14459</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2827</v>
+        <v>3141</v>
       </c>
       <c r="C4" t="n">
-        <v>6104</v>
+        <v>4982</v>
       </c>
       <c r="D4" t="n">
-        <v>11604</v>
+        <v>13131</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2246</v>
+        <v>2532</v>
       </c>
       <c r="C5" t="n">
-        <v>8214</v>
+        <v>6381</v>
       </c>
       <c r="D5" t="n">
-        <v>6056</v>
+        <v>6625</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1230</v>
+        <v>1383</v>
       </c>
       <c r="C6" t="n">
-        <v>7682</v>
+        <v>6265</v>
       </c>
       <c r="D6" t="n">
-        <v>2102</v>
+        <v>2175</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>272</v>
+        <v>318</v>
       </c>
       <c r="C7" t="n">
-        <v>4655</v>
+        <v>4154</v>
       </c>
       <c r="D7" t="n">
-        <v>750</v>
+        <v>760</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="C8" t="n">
-        <v>2169</v>
+        <v>1912</v>
       </c>
       <c r="D8" t="n">
-        <v>411</v>
+        <v>432</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C9" t="n">
-        <v>642</v>
+        <v>614</v>
       </c>
       <c r="D9" t="n">
-        <v>294</v>
+        <v>301</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C10" t="n">
         <v>230</v>
       </c>
       <c r="D10" t="n">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>132</v>
+        <v>139</v>
       </c>
       <c r="D11" t="n">
-        <v>134</v>
+        <v>136</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="D12" t="n">
-        <v>91</v>
+        <v>95</v>
       </c>
     </row>
     <row r="13">
@@ -3425,10 +3425,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D13" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="14">
@@ -3442,7 +3442,7 @@
         <v>37</v>
       </c>
       <c r="D14" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="15">
@@ -3453,10 +3453,10 @@
         <v>3</v>
       </c>
       <c r="C15" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D15" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="16">
@@ -3467,7 +3467,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D16" t="n">
         <v>9</v>
@@ -3481,7 +3481,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D17" t="n">
         <v>1</v>
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3839</v>
+        <v>4502</v>
       </c>
       <c r="C2" t="n">
-        <v>6680</v>
+        <v>6715</v>
       </c>
       <c r="D2" t="n">
-        <v>10527</v>
+        <v>19214</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2015</v>
+        <v>2538</v>
       </c>
       <c r="C3" t="n">
-        <v>4641</v>
+        <v>3019</v>
       </c>
       <c r="D3" t="n">
-        <v>10677</v>
+        <v>12935</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2378</v>
+        <v>2738</v>
       </c>
       <c r="C4" t="n">
-        <v>5577</v>
+        <v>4383</v>
       </c>
       <c r="D4" t="n">
-        <v>11281</v>
+        <v>12796</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2226</v>
+        <v>2527</v>
       </c>
       <c r="C5" t="n">
-        <v>7192</v>
+        <v>5670</v>
       </c>
       <c r="D5" t="n">
-        <v>6617</v>
+        <v>7360</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1461</v>
+        <v>1655</v>
       </c>
       <c r="C6" t="n">
-        <v>7821</v>
+        <v>6256</v>
       </c>
       <c r="D6" t="n">
-        <v>2568</v>
+        <v>2744</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>506</v>
+        <v>588</v>
       </c>
       <c r="C7" t="n">
-        <v>5826</v>
+        <v>4959</v>
       </c>
       <c r="D7" t="n">
-        <v>901</v>
+        <v>932</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>101</v>
+        <v>118</v>
       </c>
       <c r="C8" t="n">
-        <v>3020</v>
+        <v>2742</v>
       </c>
       <c r="D8" t="n">
-        <v>443</v>
+        <v>466</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C9" t="n">
-        <v>1141</v>
+        <v>1052</v>
       </c>
       <c r="D9" t="n">
-        <v>302</v>
+        <v>312</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C10" t="n">
-        <v>353</v>
+        <v>348</v>
       </c>
       <c r="D10" t="n">
-        <v>186</v>
+        <v>189</v>
       </c>
     </row>
     <row r="11">
@@ -3708,7 +3708,7 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="D11" t="n">
         <v>137</v>
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="D12" t="n">
-        <v>93</v>
+        <v>97</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D13" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="14">
@@ -3753,7 +3753,7 @@
         <v>39</v>
       </c>
       <c r="D14" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="15">
@@ -3764,10 +3764,10 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D15" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="16">
@@ -3778,7 +3778,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="D16" t="n">
         <v>8</v>
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5227</v>
+        <v>4588</v>
       </c>
       <c r="C2" t="n">
-        <v>8128</v>
+        <v>4513</v>
       </c>
       <c r="D2" t="n">
-        <v>6250</v>
+        <v>9100</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2775</v>
+        <v>3185</v>
       </c>
       <c r="C2" t="n">
-        <v>3847</v>
+        <v>3760</v>
       </c>
       <c r="D2" t="n">
-        <v>7832</v>
+        <v>14142</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2793</v>
+        <v>3457</v>
       </c>
       <c r="C3" t="n">
-        <v>5506</v>
+        <v>4162</v>
       </c>
       <c r="D3" t="n">
-        <v>11597</v>
+        <v>14507</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3271</v>
+        <v>3711</v>
       </c>
       <c r="C4" t="n">
-        <v>8077</v>
+        <v>6242</v>
       </c>
       <c r="D4" t="n">
-        <v>11659</v>
+        <v>13120</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1391</v>
+        <v>1622</v>
       </c>
       <c r="C5" t="n">
-        <v>10834</v>
+        <v>8599</v>
       </c>
       <c r="D5" t="n">
-        <v>6022</v>
+        <v>6714</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>467</v>
+        <v>543</v>
       </c>
       <c r="C6" t="n">
-        <v>7165</v>
+        <v>6147</v>
       </c>
       <c r="D6" t="n">
-        <v>2026</v>
+        <v>2139</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>93</v>
+        <v>109</v>
       </c>
       <c r="C7" t="n">
-        <v>2959</v>
+        <v>2687</v>
       </c>
       <c r="D7" t="n">
-        <v>548</v>
+        <v>575</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C8" t="n">
-        <v>1118</v>
+        <v>1030</v>
       </c>
       <c r="D8" t="n">
-        <v>295</v>
+        <v>305</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C9" t="n">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="D9" t="n">
-        <v>182</v>
+        <v>185</v>
       </c>
     </row>
     <row r="10">
@@ -4316,7 +4316,7 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="D10" t="n">
         <v>134</v>
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="D11" t="n">
-        <v>91</v>
+        <v>95</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D12" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="13">
@@ -4361,7 +4361,7 @@
         <v>38</v>
       </c>
       <c r="D13" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="14">
@@ -4372,10 +4372,10 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D14" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="15">
@@ -4386,7 +4386,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="D15" t="n">
         <v>7</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5777</v>
+        <v>6524</v>
       </c>
       <c r="C2" t="n">
-        <v>5558</v>
+        <v>5182</v>
       </c>
       <c r="D2" t="n">
-        <v>19703</v>
+        <v>8890</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2221</v>
+        <v>1950</v>
       </c>
       <c r="C3" t="n">
-        <v>4096</v>
+        <v>2310</v>
       </c>
       <c r="D3" t="n">
-        <v>1689</v>
+        <v>2168</v>
       </c>
     </row>
     <row r="4">
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4959</v>
+        <v>4395</v>
       </c>
       <c r="C2" t="n">
-        <v>3731</v>
+        <v>3597</v>
       </c>
       <c r="D2" t="n">
-        <v>23961</v>
+        <v>18267</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3284</v>
+        <v>3528</v>
       </c>
       <c r="C3" t="n">
-        <v>4245</v>
+        <v>3412</v>
       </c>
       <c r="D3" t="n">
-        <v>4591</v>
+        <v>3137</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>999</v>
+        <v>880</v>
       </c>
       <c r="C4" t="n">
-        <v>2443</v>
+        <v>1418</v>
       </c>
       <c r="D4" t="n">
-        <v>1521</v>
+        <v>1618</v>
       </c>
     </row>
     <row r="5">
@@ -4865,10 +4865,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C5" t="n">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="D5" t="n">
         <v>1186</v>
@@ -4879,7 +4879,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="C6" t="n">
         <v>411</v>
@@ -4893,7 +4893,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="C7" t="n">
         <v>409</v>
@@ -4910,7 +4910,7 @@
         <v>115</v>
       </c>
       <c r="C8" t="n">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="D8" t="n">
         <v>441</v>
@@ -4924,7 +4924,7 @@
         <v>84</v>
       </c>
       <c r="C9" t="n">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="D9" t="n">
         <v>363</v>
@@ -4938,7 +4938,7 @@
         <v>63</v>
       </c>
       <c r="C10" t="n">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="D10" t="n">
         <v>352</v>
@@ -4949,7 +4949,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C11" t="n">
         <v>166</v>
@@ -4983,7 +4983,7 @@
         <v>103</v>
       </c>
       <c r="D13" t="n">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="14">
@@ -4997,7 +4997,7 @@
         <v>83</v>
       </c>
       <c r="D14" t="n">
-        <v>146</v>
+        <v>148</v>
       </c>
     </row>
     <row r="15">
@@ -5008,7 +5008,7 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D15" t="n">
         <v>120</v>
@@ -5022,7 +5022,7 @@
         <v>13</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D16" t="n">
         <v>98</v>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4579</v>
+        <v>5739</v>
       </c>
       <c r="C2" t="n">
-        <v>5656</v>
+        <v>4566</v>
       </c>
       <c r="D2" t="n">
-        <v>26771</v>
+        <v>27578</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3370</v>
+        <v>3260</v>
       </c>
       <c r="C3" t="n">
-        <v>3431</v>
+        <v>3069</v>
       </c>
       <c r="D3" t="n">
-        <v>7359</v>
+        <v>5331</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1822</v>
+        <v>1892</v>
       </c>
       <c r="C4" t="n">
-        <v>3412</v>
+        <v>2504</v>
       </c>
       <c r="D4" t="n">
-        <v>2064</v>
+        <v>1844</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>461</v>
+        <v>422</v>
       </c>
       <c r="C5" t="n">
-        <v>1431</v>
+        <v>882</v>
       </c>
       <c r="D5" t="n">
-        <v>1199</v>
+        <v>1232</v>
       </c>
     </row>
     <row r="6">
@@ -5190,10 +5190,10 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="C6" t="n">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="D6" t="n">
         <v>910</v>
@@ -5204,7 +5204,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C7" t="n">
         <v>409</v>
@@ -5221,7 +5221,7 @@
         <v>125</v>
       </c>
       <c r="C8" t="n">
-        <v>358</v>
+        <v>354</v>
       </c>
       <c r="D8" t="n">
         <v>462</v>
@@ -5232,7 +5232,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C9" t="n">
         <v>268</v>
@@ -5246,10 +5246,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C10" t="n">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="D10" t="n">
         <v>346</v>
@@ -5263,7 +5263,7 @@
         <v>47</v>
       </c>
       <c r="C11" t="n">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="D11" t="n">
         <v>280</v>
@@ -5274,13 +5274,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C12" t="n">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D12" t="n">
-        <v>213</v>
+        <v>211</v>
       </c>
     </row>
     <row r="13">
@@ -5305,10 +5305,10 @@
         <v>15</v>
       </c>
       <c r="C14" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D14" t="n">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="15">
@@ -5319,10 +5319,10 @@
         <v>13</v>
       </c>
       <c r="C15" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D15" t="n">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="16">
@@ -5333,7 +5333,7 @@
         <v>12</v>
       </c>
       <c r="C16" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D16" t="n">
         <v>99</v>
@@ -5350,7 +5350,7 @@
         <v>68</v>
       </c>
       <c r="D17" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="18">
@@ -5361,10 +5361,10 @@
         <v>10</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D18" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="19">
@@ -5375,7 +5375,7 @@
         <v>10</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D19" t="n">
         <v>41</v>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6117</v>
+        <v>5967</v>
       </c>
       <c r="C2" t="n">
-        <v>8095</v>
+        <v>7231</v>
       </c>
       <c r="D2" t="n">
-        <v>22627</v>
+        <v>31925</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3243</v>
+        <v>3629</v>
       </c>
       <c r="C3" t="n">
-        <v>3983</v>
+        <v>3348</v>
       </c>
       <c r="D3" t="n">
-        <v>9791</v>
+        <v>8337</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2203</v>
+        <v>2175</v>
       </c>
       <c r="C4" t="n">
-        <v>3351</v>
+        <v>2761</v>
       </c>
       <c r="D4" t="n">
-        <v>2967</v>
+        <v>2406</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>937</v>
+        <v>959</v>
       </c>
       <c r="C5" t="n">
-        <v>2414</v>
+        <v>1720</v>
       </c>
       <c r="D5" t="n">
-        <v>1300</v>
+        <v>1306</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>266</v>
+        <v>248</v>
       </c>
       <c r="C6" t="n">
-        <v>872</v>
+        <v>591</v>
       </c>
       <c r="D6" t="n">
-        <v>947</v>
+        <v>944</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="C7" t="n">
         <v>354</v>
       </c>
       <c r="D7" t="n">
-        <v>659</v>
+        <v>668</v>
       </c>
     </row>
     <row r="8">
@@ -5529,10 +5529,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C8" t="n">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="D8" t="n">
         <v>484</v>
@@ -5543,10 +5543,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="C9" t="n">
-        <v>310</v>
+        <v>305</v>
       </c>
       <c r="D9" t="n">
         <v>378</v>
@@ -5557,10 +5557,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C10" t="n">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="D10" t="n">
         <v>346</v>
@@ -5574,10 +5574,10 @@
         <v>50</v>
       </c>
       <c r="C11" t="n">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="D11" t="n">
-        <v>286</v>
+        <v>284</v>
       </c>
     </row>
     <row r="12">
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C12" t="n">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="D12" t="n">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="13">
@@ -5616,10 +5616,10 @@
         <v>15</v>
       </c>
       <c r="C14" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D14" t="n">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="15">
@@ -5630,10 +5630,10 @@
         <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D15" t="n">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="16">
@@ -5647,7 +5647,7 @@
         <v>73</v>
       </c>
       <c r="D16" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="17">
@@ -5658,7 +5658,7 @@
         <v>10</v>
       </c>
       <c r="C17" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D17" t="n">
         <v>79</v>
@@ -5672,10 +5672,10 @@
         <v>9</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D18" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="19">
@@ -5689,7 +5689,7 @@
         <v>62</v>
       </c>
       <c r="D19" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="20">
@@ -5700,7 +5700,7 @@
         <v>7</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D20" t="n">
         <v>24</v>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5983</v>
+        <v>5930</v>
       </c>
       <c r="C2" t="n">
-        <v>9570</v>
+        <v>9222</v>
       </c>
       <c r="D2" t="n">
-        <v>36038</v>
+        <v>29798</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3363</v>
+        <v>3482</v>
       </c>
       <c r="C3" t="n">
-        <v>4984</v>
+        <v>4396</v>
       </c>
       <c r="D3" t="n">
-        <v>10399</v>
+        <v>10663</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1679</v>
+        <v>1800</v>
       </c>
       <c r="C4" t="n">
-        <v>3005</v>
+        <v>2534</v>
       </c>
       <c r="D4" t="n">
-        <v>3597</v>
+        <v>2961</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>815</v>
+        <v>828</v>
       </c>
       <c r="C5" t="n">
-        <v>2123</v>
+        <v>1647</v>
       </c>
       <c r="D5" t="n">
-        <v>1244</v>
+        <v>1189</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="C6" t="n">
-        <v>1111</v>
+        <v>789</v>
       </c>
       <c r="D6" t="n">
-        <v>766</v>
+        <v>758</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C7" t="n">
-        <v>386</v>
+        <v>300</v>
       </c>
       <c r="D7" t="n">
-        <v>513</v>
+        <v>525</v>
       </c>
     </row>
     <row r="8">
@@ -5843,10 +5843,10 @@
         <v>58</v>
       </c>
       <c r="C8" t="n">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="D8" t="n">
-        <v>364</v>
+        <v>361</v>
       </c>
     </row>
     <row r="9">
@@ -5854,13 +5854,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C9" t="n">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="D9" t="n">
-        <v>270</v>
+        <v>273</v>
       </c>
     </row>
     <row r="10">
@@ -5871,7 +5871,7 @@
         <v>31</v>
       </c>
       <c r="C10" t="n">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D10" t="n">
         <v>237</v>
@@ -5885,10 +5885,10 @@
         <v>21</v>
       </c>
       <c r="C11" t="n">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="D11" t="n">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="12">
@@ -5899,10 +5899,10 @@
         <v>14</v>
       </c>
       <c r="C12" t="n">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="D12" t="n">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="13">
@@ -5913,7 +5913,7 @@
         <v>9</v>
       </c>
       <c r="C13" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D13" t="n">
         <v>116</v>
@@ -5927,7 +5927,7 @@
         <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D14" t="n">
         <v>97</v>
@@ -5958,7 +5958,7 @@
         <v>38</v>
       </c>
       <c r="D16" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17">
@@ -5969,7 +5969,7 @@
         <v>3</v>
       </c>
       <c r="C17" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D17" t="n">
         <v>50</v>
@@ -5980,7 +5980,7 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C18" t="n">
         <v>33</v>
@@ -6000,7 +6000,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="20">
@@ -6025,7 +6025,7 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D21" t="n">
         <v>6</v>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4473</v>
+        <v>5982</v>
       </c>
       <c r="C2" t="n">
-        <v>7504</v>
+        <v>7220</v>
       </c>
       <c r="D2" t="n">
-        <v>31916</v>
+        <v>24089</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3883</v>
+        <v>3926</v>
       </c>
       <c r="C3" t="n">
-        <v>6593</v>
+        <v>6272</v>
       </c>
       <c r="D3" t="n">
-        <v>13940</v>
+        <v>13228</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2219</v>
+        <v>2338</v>
       </c>
       <c r="C4" t="n">
-        <v>4110</v>
+        <v>3643</v>
       </c>
       <c r="D4" t="n">
-        <v>4824</v>
+        <v>4497</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1106</v>
+        <v>1180</v>
       </c>
       <c r="C5" t="n">
-        <v>2603</v>
+        <v>2149</v>
       </c>
       <c r="D5" t="n">
-        <v>1680</v>
+        <v>1498</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>514</v>
+        <v>517</v>
       </c>
       <c r="C6" t="n">
-        <v>1680</v>
+        <v>1281</v>
       </c>
       <c r="D6" t="n">
-        <v>839</v>
+        <v>833</v>
       </c>
     </row>
     <row r="7">
@@ -6140,10 +6140,10 @@
         <v>172</v>
       </c>
       <c r="C7" t="n">
-        <v>797</v>
+        <v>582</v>
       </c>
       <c r="D7" t="n">
-        <v>557</v>
+        <v>565</v>
       </c>
     </row>
     <row r="8">
@@ -6154,10 +6154,10 @@
         <v>67</v>
       </c>
       <c r="C8" t="n">
-        <v>312</v>
+        <v>266</v>
       </c>
       <c r="D8" t="n">
-        <v>388</v>
+        <v>384</v>
       </c>
     </row>
     <row r="9">
@@ -6168,10 +6168,10 @@
         <v>47</v>
       </c>
       <c r="C9" t="n">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="D9" t="n">
-        <v>281</v>
+        <v>286</v>
       </c>
     </row>
     <row r="10">
@@ -6199,7 +6199,7 @@
         <v>132</v>
       </c>
       <c r="D11" t="n">
-        <v>199</v>
+        <v>196</v>
       </c>
     </row>
     <row r="12">
@@ -6210,10 +6210,10 @@
         <v>15</v>
       </c>
       <c r="C12" t="n">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="D12" t="n">
-        <v>152</v>
+        <v>154</v>
       </c>
     </row>
     <row r="13">
@@ -6224,7 +6224,7 @@
         <v>10</v>
       </c>
       <c r="C13" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="D13" t="n">
         <v>119</v>
@@ -6235,13 +6235,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C14" t="n">
         <v>64</v>
       </c>
       <c r="D14" t="n">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="15">
@@ -6255,7 +6255,7 @@
         <v>50</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="16">
@@ -6269,7 +6269,7 @@
         <v>40</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="17">
@@ -6280,10 +6280,10 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="18">
@@ -6297,7 +6297,7 @@
         <v>33</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19">
@@ -6305,13 +6305,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C19" t="n">
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="20">
@@ -6336,7 +6336,7 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="D21" t="n">
         <v>7</v>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4207</v>
+        <v>5282</v>
       </c>
       <c r="C2" t="n">
-        <v>6086</v>
+        <v>4380</v>
       </c>
       <c r="D2" t="n">
-        <v>27620</v>
+        <v>28012</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3440</v>
+        <v>4065</v>
       </c>
       <c r="C3" t="n">
-        <v>6136</v>
+        <v>5874</v>
       </c>
       <c r="D3" t="n">
-        <v>15812</v>
+        <v>14013</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2604</v>
+        <v>2688</v>
       </c>
       <c r="C4" t="n">
-        <v>5430</v>
+        <v>5081</v>
       </c>
       <c r="D4" t="n">
-        <v>6427</v>
+        <v>5993</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1459</v>
+        <v>1553</v>
       </c>
       <c r="C5" t="n">
-        <v>3373</v>
+        <v>2915</v>
       </c>
       <c r="D5" t="n">
-        <v>2186</v>
+        <v>2028</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>731</v>
+        <v>770</v>
       </c>
       <c r="C6" t="n">
-        <v>2131</v>
+        <v>1740</v>
       </c>
       <c r="D6" t="n">
-        <v>980</v>
+        <v>934</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="C7" t="n">
-        <v>1263</v>
+        <v>958</v>
       </c>
       <c r="D7" t="n">
-        <v>595</v>
+        <v>609</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C8" t="n">
-        <v>559</v>
+        <v>430</v>
       </c>
       <c r="D8" t="n">
-        <v>413</v>
+        <v>412</v>
       </c>
     </row>
     <row r="9">
@@ -6479,10 +6479,10 @@
         <v>51</v>
       </c>
       <c r="C9" t="n">
-        <v>260</v>
+        <v>236</v>
       </c>
       <c r="D9" t="n">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="10">
@@ -6493,10 +6493,10 @@
         <v>36</v>
       </c>
       <c r="C10" t="n">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="D10" t="n">
-        <v>241</v>
+        <v>245</v>
       </c>
     </row>
     <row r="11">
@@ -6507,10 +6507,10 @@
         <v>25</v>
       </c>
       <c r="C11" t="n">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="D11" t="n">
-        <v>203</v>
+        <v>200</v>
       </c>
     </row>
     <row r="12">
@@ -6521,10 +6521,10 @@
         <v>16</v>
       </c>
       <c r="C12" t="n">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="D12" t="n">
-        <v>155</v>
+        <v>157</v>
       </c>
     </row>
     <row r="13">
@@ -6535,7 +6535,7 @@
         <v>10</v>
       </c>
       <c r="C13" t="n">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="D13" t="n">
         <v>122</v>
@@ -6549,10 +6549,10 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D14" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="15">
@@ -6566,7 +6566,7 @@
         <v>55</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="16">
@@ -6580,7 +6580,7 @@
         <v>43</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="17">
@@ -6591,10 +6591,10 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="18">
@@ -6605,10 +6605,10 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19">
@@ -6622,7 +6622,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="20">
@@ -6630,7 +6630,7 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
         <v>29</v>
@@ -6647,7 +6647,7 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="D21" t="n">
         <v>8</v>

--- a/output/yearly_population_iteration_93_growth_param_0.5.xlsx
+++ b/output/yearly_population_iteration_93_growth_param_0.5.xlsx
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5689</v>
+        <v>6964</v>
       </c>
       <c r="C2" t="n">
-        <v>6040</v>
+        <v>13313</v>
       </c>
       <c r="D2" t="n">
-        <v>37056</v>
+        <v>29117</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3821</v>
+        <v>3950</v>
       </c>
       <c r="C3" t="n">
-        <v>4443</v>
+        <v>5363</v>
       </c>
       <c r="D3" t="n">
-        <v>15154</v>
+        <v>11439</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2887</v>
+        <v>2638</v>
       </c>
       <c r="C4" t="n">
-        <v>5401</v>
+        <v>4044</v>
       </c>
       <c r="D4" t="n">
-        <v>7273</v>
+        <v>6601</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1834</v>
+        <v>1835</v>
       </c>
       <c r="C5" t="n">
-        <v>3949</v>
+        <v>2553</v>
       </c>
       <c r="D5" t="n">
-        <v>2632</v>
+        <v>2844</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1044</v>
+        <v>1140</v>
       </c>
       <c r="C6" t="n">
-        <v>2318</v>
+        <v>2050</v>
       </c>
       <c r="D6" t="n">
-        <v>1110</v>
+        <v>1184</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>466</v>
+        <v>565</v>
       </c>
       <c r="C7" t="n">
-        <v>1348</v>
+        <v>1523</v>
       </c>
       <c r="D7" t="n">
-        <v>650</v>
+        <v>656</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>175</v>
+        <v>211</v>
       </c>
       <c r="C8" t="n">
-        <v>679</v>
+        <v>850</v>
       </c>
       <c r="D8" t="n">
-        <v>440</v>
+        <v>439</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="C9" t="n">
-        <v>327</v>
+        <v>384</v>
       </c>
       <c r="D9" t="n">
-        <v>311</v>
+        <v>303</v>
       </c>
     </row>
     <row r="10">
@@ -895,7 +895,7 @@
         <v>39</v>
       </c>
       <c r="C10" t="n">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="D10" t="n">
         <v>247</v>
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C11" t="n">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="D11" t="n">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="12">
@@ -923,7 +923,7 @@
         <v>17</v>
       </c>
       <c r="C12" t="n">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D12" t="n">
         <v>159</v>
@@ -937,7 +937,7 @@
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="D13" t="n">
         <v>125</v>
@@ -968,7 +968,7 @@
         <v>60</v>
       </c>
       <c r="D15" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="16">
@@ -982,7 +982,7 @@
         <v>47</v>
       </c>
       <c r="D16" t="n">
-        <v>67</v>
+        <v>65</v>
       </c>
     </row>
     <row r="17">
@@ -996,7 +996,7 @@
         <v>38</v>
       </c>
       <c r="D17" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
     </row>
     <row r="18">
@@ -1024,7 +1024,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="20">
@@ -1038,7 +1038,7 @@
         <v>29</v>
       </c>
       <c r="D20" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="21">
@@ -1049,7 +1049,7 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D21" t="n">
         <v>9</v>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6771</v>
+        <v>7122</v>
       </c>
       <c r="C2" t="n">
-        <v>7834</v>
+        <v>7024</v>
       </c>
       <c r="D2" t="n">
-        <v>30830</v>
+        <v>25957</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3812</v>
+        <v>4313</v>
       </c>
       <c r="C3" t="n">
-        <v>4554</v>
+        <v>8009</v>
       </c>
       <c r="D3" t="n">
-        <v>17114</v>
+        <v>13197</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2851</v>
+        <v>2750</v>
       </c>
       <c r="C4" t="n">
-        <v>4767</v>
+        <v>4618</v>
       </c>
       <c r="D4" t="n">
-        <v>8268</v>
+        <v>7236</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2025</v>
+        <v>1944</v>
       </c>
       <c r="C5" t="n">
-        <v>4563</v>
+        <v>3191</v>
       </c>
       <c r="D5" t="n">
-        <v>3309</v>
+        <v>3343</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1266</v>
+        <v>1337</v>
       </c>
       <c r="C6" t="n">
-        <v>3023</v>
+        <v>2265</v>
       </c>
       <c r="D6" t="n">
-        <v>1318</v>
+        <v>1438</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>647</v>
+        <v>734</v>
       </c>
       <c r="C7" t="n">
-        <v>1794</v>
+        <v>1750</v>
       </c>
       <c r="D7" t="n">
-        <v>715</v>
+        <v>725</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>262</v>
+        <v>321</v>
       </c>
       <c r="C8" t="n">
-        <v>967</v>
+        <v>1153</v>
       </c>
       <c r="D8" t="n">
-        <v>462</v>
+        <v>468</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>98</v>
+        <v>117</v>
       </c>
       <c r="C9" t="n">
-        <v>478</v>
+        <v>581</v>
       </c>
       <c r="D9" t="n">
-        <v>326</v>
+        <v>319</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="C10" t="n">
-        <v>257</v>
+        <v>287</v>
       </c>
       <c r="D10" t="n">
-        <v>250</v>
+        <v>249</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C11" t="n">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="D11" t="n">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="12">
@@ -1245,7 +1245,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C13" t="n">
         <v>110</v>
@@ -1259,10 +1259,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C14" t="n">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="D14" t="n">
         <v>100</v>
@@ -1279,7 +1279,7 @@
         <v>65</v>
       </c>
       <c r="D15" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="16">
@@ -1290,10 +1290,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D16" t="n">
-        <v>67</v>
+        <v>65</v>
       </c>
     </row>
     <row r="17">
@@ -1307,7 +1307,7 @@
         <v>40</v>
       </c>
       <c r="D17" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
     </row>
     <row r="18">
@@ -1318,7 +1318,7 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D18" t="n">
         <v>39</v>
@@ -1335,7 +1335,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="20">
@@ -1349,7 +1349,7 @@
         <v>29</v>
       </c>
       <c r="D20" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="21">
@@ -1360,7 +1360,7 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D21" t="n">
         <v>10</v>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7947</v>
+        <v>8002</v>
       </c>
       <c r="C2" t="n">
-        <v>8012</v>
+        <v>7247</v>
       </c>
       <c r="D2" t="n">
-        <v>35179</v>
+        <v>25473</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4093</v>
+        <v>4483</v>
       </c>
       <c r="C3" t="n">
-        <v>5262</v>
+        <v>6695</v>
       </c>
       <c r="D3" t="n">
-        <v>17746</v>
+        <v>13964</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2772</v>
+        <v>2899</v>
       </c>
       <c r="C4" t="n">
-        <v>4525</v>
+        <v>6084</v>
       </c>
       <c r="D4" t="n">
-        <v>9296</v>
+        <v>7862</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2101</v>
+        <v>2045</v>
       </c>
       <c r="C5" t="n">
-        <v>4558</v>
+        <v>3724</v>
       </c>
       <c r="D5" t="n">
-        <v>3970</v>
+        <v>3839</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1440</v>
+        <v>1455</v>
       </c>
       <c r="C6" t="n">
-        <v>3616</v>
+        <v>2621</v>
       </c>
       <c r="D6" t="n">
-        <v>1574</v>
+        <v>1679</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>815</v>
+        <v>885</v>
       </c>
       <c r="C7" t="n">
-        <v>2311</v>
+        <v>1971</v>
       </c>
       <c r="D7" t="n">
-        <v>796</v>
+        <v>822</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>365</v>
+        <v>433</v>
       </c>
       <c r="C8" t="n">
-        <v>1289</v>
+        <v>1386</v>
       </c>
       <c r="D8" t="n">
-        <v>487</v>
+        <v>493</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>141</v>
+        <v>174</v>
       </c>
       <c r="C9" t="n">
-        <v>664</v>
+        <v>810</v>
       </c>
       <c r="D9" t="n">
-        <v>341</v>
+        <v>336</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="C10" t="n">
-        <v>341</v>
+        <v>396</v>
       </c>
       <c r="D10" t="n">
-        <v>254</v>
+        <v>252</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C11" t="n">
-        <v>209</v>
+        <v>223</v>
       </c>
       <c r="D11" t="n">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="12">
@@ -1542,10 +1542,10 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C12" t="n">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="D12" t="n">
         <v>163</v>
@@ -1559,7 +1559,7 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D13" t="n">
         <v>130</v>
@@ -1573,7 +1573,7 @@
         <v>7</v>
       </c>
       <c r="C14" t="n">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="D14" t="n">
         <v>101</v>
@@ -1587,7 +1587,7 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D15" t="n">
         <v>83</v>
@@ -1604,7 +1604,7 @@
         <v>54</v>
       </c>
       <c r="D16" t="n">
-        <v>67</v>
+        <v>65</v>
       </c>
     </row>
     <row r="17">
@@ -1615,10 +1615,10 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="18">
@@ -1643,10 +1643,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="20">
@@ -1660,7 +1660,7 @@
         <v>29</v>
       </c>
       <c r="D20" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="21">
@@ -1671,7 +1671,7 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D21" t="n">
         <v>11</v>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7204</v>
+        <v>7291</v>
       </c>
       <c r="C2" t="n">
-        <v>5384</v>
+        <v>4812</v>
       </c>
       <c r="D2" t="n">
-        <v>28543</v>
+        <v>20710</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5012</v>
+        <v>5410</v>
       </c>
       <c r="C3" t="n">
-        <v>7858</v>
+        <v>9749</v>
       </c>
       <c r="D3" t="n">
-        <v>19402</v>
+        <v>15412</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1941</v>
+        <v>1889</v>
       </c>
       <c r="C4" t="n">
-        <v>6938</v>
+        <v>7079</v>
       </c>
       <c r="D4" t="n">
-        <v>8863</v>
+        <v>7824</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1330</v>
+        <v>1344</v>
       </c>
       <c r="C5" t="n">
-        <v>3543</v>
+        <v>2568</v>
       </c>
       <c r="D5" t="n">
-        <v>2647</v>
+        <v>2714</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>753</v>
+        <v>817</v>
       </c>
       <c r="C6" t="n">
-        <v>2264</v>
+        <v>1931</v>
       </c>
       <c r="D6" t="n">
-        <v>780</v>
+        <v>805</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>337</v>
+        <v>400</v>
       </c>
       <c r="C7" t="n">
-        <v>1263</v>
+        <v>1358</v>
       </c>
       <c r="D7" t="n">
-        <v>477</v>
+        <v>483</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>130</v>
+        <v>160</v>
       </c>
       <c r="C8" t="n">
-        <v>650</v>
+        <v>793</v>
       </c>
       <c r="D8" t="n">
-        <v>334</v>
+        <v>329</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="C9" t="n">
-        <v>334</v>
+        <v>388</v>
       </c>
       <c r="D9" t="n">
-        <v>248</v>
+        <v>246</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C10" t="n">
-        <v>204</v>
+        <v>218</v>
       </c>
       <c r="D10" t="n">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="11">
@@ -1839,10 +1839,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C11" t="n">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="D11" t="n">
         <v>159</v>
@@ -1856,7 +1856,7 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D12" t="n">
         <v>127</v>
@@ -1870,7 +1870,7 @@
         <v>6</v>
       </c>
       <c r="C13" t="n">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="D13" t="n">
         <v>98</v>
@@ -1884,7 +1884,7 @@
         <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="D14" t="n">
         <v>81</v>
@@ -1901,7 +1901,7 @@
         <v>52</v>
       </c>
       <c r="D15" t="n">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="16">
@@ -1912,10 +1912,10 @@
         <v>1</v>
       </c>
       <c r="C16" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D16" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="17">
@@ -1940,10 +1940,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D18" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="19">
@@ -1957,7 +1957,7 @@
         <v>28</v>
       </c>
       <c r="D19" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="20">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4360</v>
+        <v>4482</v>
       </c>
       <c r="C2" t="n">
-        <v>2557</v>
+        <v>2282</v>
       </c>
       <c r="D2" t="n">
-        <v>19972</v>
+        <v>14291</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5138</v>
+        <v>5399</v>
       </c>
       <c r="C3" t="n">
-        <v>6054</v>
+        <v>6719</v>
       </c>
       <c r="D3" t="n">
-        <v>19755</v>
+        <v>15410</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2718</v>
+        <v>2834</v>
       </c>
       <c r="C4" t="n">
-        <v>7501</v>
+        <v>8417</v>
       </c>
       <c r="D4" t="n">
-        <v>10382</v>
+        <v>8826</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1486</v>
+        <v>1490</v>
       </c>
       <c r="C5" t="n">
-        <v>5073</v>
+        <v>4586</v>
       </c>
       <c r="D5" t="n">
-        <v>3393</v>
+        <v>3396</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>898</v>
+        <v>978</v>
       </c>
       <c r="C6" t="n">
-        <v>2833</v>
+        <v>2280</v>
       </c>
       <c r="D6" t="n">
-        <v>972</v>
+        <v>1002</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>319</v>
+        <v>379</v>
       </c>
       <c r="C7" t="n">
-        <v>1658</v>
+        <v>1626</v>
       </c>
       <c r="D7" t="n">
-        <v>521</v>
+        <v>525</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>110</v>
+        <v>134</v>
       </c>
       <c r="C8" t="n">
-        <v>847</v>
+        <v>1013</v>
       </c>
       <c r="D8" t="n">
-        <v>345</v>
+        <v>343</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="C9" t="n">
-        <v>393</v>
+        <v>453</v>
       </c>
       <c r="D9" t="n">
-        <v>260</v>
+        <v>258</v>
       </c>
     </row>
     <row r="10">
@@ -2136,10 +2136,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C10" t="n">
-        <v>227</v>
+        <v>236</v>
       </c>
       <c r="D10" t="n">
         <v>212</v>
@@ -2156,7 +2156,7 @@
         <v>171</v>
       </c>
       <c r="D11" t="n">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="12">
@@ -2167,10 +2167,10 @@
         <v>5</v>
       </c>
       <c r="C12" t="n">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D12" t="n">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="13">
@@ -2181,7 +2181,7 @@
         <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="D13" t="n">
         <v>101</v>
@@ -2198,7 +2198,7 @@
         <v>50</v>
       </c>
       <c r="D14" t="n">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="15">
@@ -2209,10 +2209,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D15" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="16">
@@ -2237,10 +2237,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D17" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="18">
@@ -2254,7 +2254,7 @@
         <v>27</v>
       </c>
       <c r="D18" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="19">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6185</v>
+        <v>4566</v>
       </c>
       <c r="C2" t="n">
-        <v>8305</v>
+        <v>8169</v>
       </c>
       <c r="D2" t="n">
-        <v>17234</v>
+        <v>22445</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4029</v>
+        <v>4199</v>
       </c>
       <c r="C3" t="n">
-        <v>3815</v>
+        <v>4017</v>
       </c>
       <c r="D3" t="n">
-        <v>18427</v>
+        <v>14188</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3271</v>
+        <v>3426</v>
       </c>
       <c r="C4" t="n">
-        <v>6680</v>
+        <v>7377</v>
       </c>
       <c r="D4" t="n">
-        <v>11686</v>
+        <v>9695</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1791</v>
+        <v>1833</v>
       </c>
       <c r="C5" t="n">
-        <v>6132</v>
+        <v>6366</v>
       </c>
       <c r="D5" t="n">
-        <v>4430</v>
+        <v>4178</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1055</v>
+        <v>1105</v>
       </c>
       <c r="C6" t="n">
-        <v>3864</v>
+        <v>3363</v>
       </c>
       <c r="D6" t="n">
-        <v>1330</v>
+        <v>1356</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>488</v>
+        <v>552</v>
       </c>
       <c r="C7" t="n">
-        <v>2175</v>
+        <v>1936</v>
       </c>
       <c r="D7" t="n">
-        <v>581</v>
+        <v>589</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>163</v>
+        <v>196</v>
       </c>
       <c r="C8" t="n">
-        <v>1196</v>
+        <v>1280</v>
       </c>
       <c r="D8" t="n">
-        <v>369</v>
+        <v>364</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="C9" t="n">
-        <v>578</v>
+        <v>676</v>
       </c>
       <c r="D9" t="n">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C10" t="n">
-        <v>289</v>
+        <v>319</v>
       </c>
       <c r="D10" t="n">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="11">
@@ -2464,7 +2464,7 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="D11" t="n">
         <v>169</v>
@@ -2478,10 +2478,10 @@
         <v>5</v>
       </c>
       <c r="C12" t="n">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D12" t="n">
-        <v>133</v>
+        <v>135</v>
       </c>
     </row>
     <row r="13">
@@ -2492,7 +2492,7 @@
         <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D13" t="n">
         <v>102</v>
@@ -2506,10 +2506,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D14" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="15">
@@ -2520,7 +2520,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D15" t="n">
         <v>48</v>
@@ -2548,10 +2548,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D17" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="18">
@@ -2562,10 +2562,10 @@
         <v>6</v>
       </c>
       <c r="C18" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D18" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="19">
@@ -2576,7 +2576,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D19" t="n">
         <v>7</v>
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3602</v>
+        <v>2670</v>
       </c>
       <c r="C2" t="n">
-        <v>3741</v>
+        <v>3696</v>
       </c>
       <c r="D2" t="n">
-        <v>11923</v>
+        <v>15455</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4402</v>
+        <v>4173</v>
       </c>
       <c r="C3" t="n">
-        <v>5267</v>
+        <v>5343</v>
       </c>
       <c r="D3" t="n">
-        <v>17851</v>
+        <v>14772</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3616</v>
+        <v>3777</v>
       </c>
       <c r="C4" t="n">
-        <v>6256</v>
+        <v>6770</v>
       </c>
       <c r="D4" t="n">
-        <v>12538</v>
+        <v>10296</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1876</v>
+        <v>1923</v>
       </c>
       <c r="C5" t="n">
-        <v>7101</v>
+        <v>7515</v>
       </c>
       <c r="D5" t="n">
-        <v>4831</v>
+        <v>4516</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>889</v>
+        <v>979</v>
       </c>
       <c r="C6" t="n">
-        <v>4708</v>
+        <v>4160</v>
       </c>
       <c r="D6" t="n">
-        <v>1309</v>
+        <v>1334</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>150</v>
+        <v>181</v>
       </c>
       <c r="C7" t="n">
-        <v>2256</v>
+        <v>2168</v>
       </c>
       <c r="D7" t="n">
-        <v>588</v>
+        <v>592</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="C8" t="n">
-        <v>953</v>
+        <v>1076</v>
       </c>
       <c r="D8" t="n">
-        <v>386</v>
+        <v>384</v>
       </c>
     </row>
     <row r="9">
@@ -2744,10 +2744,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C9" t="n">
-        <v>283</v>
+        <v>312</v>
       </c>
       <c r="D9" t="n">
         <v>293</v>
@@ -2761,7 +2761,7 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="D10" t="n">
         <v>165</v>
@@ -2775,10 +2775,10 @@
         <v>4</v>
       </c>
       <c r="C11" t="n">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D11" t="n">
-        <v>130</v>
+        <v>132</v>
       </c>
     </row>
     <row r="12">
@@ -2789,7 +2789,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D12" t="n">
         <v>99</v>
@@ -2803,10 +2803,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D13" t="n">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="14">
@@ -2817,7 +2817,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D14" t="n">
         <v>47</v>
@@ -2845,10 +2845,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D16" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="17">
@@ -2859,10 +2859,10 @@
         <v>5</v>
       </c>
       <c r="C17" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D17" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="18">
@@ -2873,7 +2873,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D18" t="n">
         <v>6</v>
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3944</v>
+        <v>3381</v>
       </c>
       <c r="C2" t="n">
-        <v>4399</v>
+        <v>4894</v>
       </c>
       <c r="D2" t="n">
-        <v>11483</v>
+        <v>19562</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3460</v>
+        <v>3016</v>
       </c>
       <c r="C3" t="n">
-        <v>4054</v>
+        <v>4050</v>
       </c>
       <c r="D3" t="n">
-        <v>15845</v>
+        <v>13995</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3441</v>
+        <v>3485</v>
       </c>
       <c r="C4" t="n">
-        <v>5651</v>
+        <v>5930</v>
       </c>
       <c r="D4" t="n">
-        <v>13023</v>
+        <v>10713</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2301</v>
+        <v>2381</v>
       </c>
       <c r="C5" t="n">
-        <v>6632</v>
+        <v>7080</v>
       </c>
       <c r="D5" t="n">
-        <v>5867</v>
+        <v>5266</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1163</v>
+        <v>1237</v>
       </c>
       <c r="C6" t="n">
-        <v>5743</v>
+        <v>5683</v>
       </c>
       <c r="D6" t="n">
-        <v>1811</v>
+        <v>1787</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>338</v>
+        <v>382</v>
       </c>
       <c r="C7" t="n">
-        <v>3308</v>
+        <v>3008</v>
       </c>
       <c r="D7" t="n">
-        <v>673</v>
+        <v>680</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="C8" t="n">
-        <v>1456</v>
+        <v>1524</v>
       </c>
       <c r="D8" t="n">
-        <v>409</v>
+        <v>408</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="C9" t="n">
-        <v>514</v>
+        <v>572</v>
       </c>
       <c r="D9" t="n">
-        <v>304</v>
+        <v>301</v>
       </c>
     </row>
     <row r="10">
@@ -3072,10 +3072,10 @@
         <v>10</v>
       </c>
       <c r="C10" t="n">
-        <v>221</v>
+        <v>233</v>
       </c>
       <c r="D10" t="n">
-        <v>173</v>
+        <v>176</v>
       </c>
     </row>
     <row r="11">
@@ -3089,7 +3089,7 @@
         <v>140</v>
       </c>
       <c r="D11" t="n">
-        <v>134</v>
+        <v>136</v>
       </c>
     </row>
     <row r="12">
@@ -3100,7 +3100,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D12" t="n">
         <v>101</v>
@@ -3117,7 +3117,7 @@
         <v>62</v>
       </c>
       <c r="D13" t="n">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="14">
@@ -3128,7 +3128,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D14" t="n">
         <v>47</v>
@@ -3145,7 +3145,7 @@
         <v>38</v>
       </c>
       <c r="D15" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="16">
@@ -3156,10 +3156,10 @@
         <v>4</v>
       </c>
       <c r="C16" t="n">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D16" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="17">
@@ -3170,7 +3170,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D17" t="n">
         <v>10</v>
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2755</v>
+        <v>2578</v>
       </c>
       <c r="C2" t="n">
-        <v>2699</v>
+        <v>2743</v>
       </c>
       <c r="D2" t="n">
-        <v>8881</v>
+        <v>14259</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3169</v>
+        <v>2748</v>
       </c>
       <c r="C3" t="n">
-        <v>3837</v>
+        <v>4017</v>
       </c>
       <c r="D3" t="n">
-        <v>14459</v>
+        <v>14058</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3141</v>
+        <v>3078</v>
       </c>
       <c r="C4" t="n">
-        <v>4982</v>
+        <v>5183</v>
       </c>
       <c r="D4" t="n">
-        <v>13131</v>
+        <v>10931</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2532</v>
+        <v>2604</v>
       </c>
       <c r="C5" t="n">
-        <v>6381</v>
+        <v>6706</v>
       </c>
       <c r="D5" t="n">
-        <v>6625</v>
+        <v>5834</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1383</v>
+        <v>1452</v>
       </c>
       <c r="C6" t="n">
-        <v>6265</v>
+        <v>6432</v>
       </c>
       <c r="D6" t="n">
-        <v>2175</v>
+        <v>2101</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>318</v>
+        <v>370</v>
       </c>
       <c r="C7" t="n">
-        <v>4154</v>
+        <v>3865</v>
       </c>
       <c r="D7" t="n">
-        <v>760</v>
+        <v>766</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>58</v>
+        <v>70</v>
       </c>
       <c r="C8" t="n">
-        <v>1912</v>
+        <v>1951</v>
       </c>
       <c r="D8" t="n">
-        <v>432</v>
+        <v>431</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C9" t="n">
-        <v>614</v>
+        <v>679</v>
       </c>
       <c r="D9" t="n">
-        <v>301</v>
+        <v>297</v>
       </c>
     </row>
     <row r="10">
@@ -3383,10 +3383,10 @@
         <v>4</v>
       </c>
       <c r="C10" t="n">
-        <v>230</v>
+        <v>241</v>
       </c>
       <c r="D10" t="n">
-        <v>177</v>
+        <v>181</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="D11" t="n">
-        <v>136</v>
+        <v>138</v>
       </c>
     </row>
     <row r="12">
@@ -3414,7 +3414,7 @@
         <v>83</v>
       </c>
       <c r="D12" t="n">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="13">
@@ -3425,10 +3425,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D13" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="14">
@@ -3442,7 +3442,7 @@
         <v>37</v>
       </c>
       <c r="D14" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="15">
@@ -3453,10 +3453,10 @@
         <v>3</v>
       </c>
       <c r="C15" t="n">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D15" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="16">
@@ -3467,7 +3467,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D16" t="n">
         <v>9</v>
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4502</v>
+        <v>4889</v>
       </c>
       <c r="C2" t="n">
-        <v>6715</v>
+        <v>4724</v>
       </c>
       <c r="D2" t="n">
-        <v>19214</v>
+        <v>15382</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2538</v>
+        <v>2258</v>
       </c>
       <c r="C3" t="n">
-        <v>3019</v>
+        <v>3091</v>
       </c>
       <c r="D3" t="n">
-        <v>12935</v>
+        <v>13296</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2738</v>
+        <v>2570</v>
       </c>
       <c r="C4" t="n">
-        <v>4383</v>
+        <v>4560</v>
       </c>
       <c r="D4" t="n">
-        <v>12796</v>
+        <v>10944</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2527</v>
+        <v>2554</v>
       </c>
       <c r="C5" t="n">
-        <v>5670</v>
+        <v>5923</v>
       </c>
       <c r="D5" t="n">
-        <v>7360</v>
+        <v>6390</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1655</v>
+        <v>1709</v>
       </c>
       <c r="C6" t="n">
-        <v>6256</v>
+        <v>6485</v>
       </c>
       <c r="D6" t="n">
-        <v>2744</v>
+        <v>2575</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>588</v>
+        <v>655</v>
       </c>
       <c r="C7" t="n">
-        <v>4959</v>
+        <v>4907</v>
       </c>
       <c r="D7" t="n">
-        <v>932</v>
+        <v>928</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>118</v>
+        <v>138</v>
       </c>
       <c r="C8" t="n">
-        <v>2742</v>
+        <v>2644</v>
       </c>
       <c r="D8" t="n">
-        <v>466</v>
+        <v>465</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="C9" t="n">
-        <v>1052</v>
+        <v>1121</v>
       </c>
       <c r="D9" t="n">
-        <v>312</v>
+        <v>308</v>
       </c>
     </row>
     <row r="10">
@@ -3694,10 +3694,10 @@
         <v>6</v>
       </c>
       <c r="C10" t="n">
-        <v>348</v>
+        <v>380</v>
       </c>
       <c r="D10" t="n">
-        <v>189</v>
+        <v>192</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="D11" t="n">
-        <v>137</v>
+        <v>139</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D12" t="n">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="13">
@@ -3739,7 +3739,7 @@
         <v>54</v>
       </c>
       <c r="D13" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="14">
@@ -3753,7 +3753,7 @@
         <v>39</v>
       </c>
       <c r="D14" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="15">
@@ -3764,10 +3764,10 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D15" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="16">
@@ -3778,7 +3778,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D16" t="n">
         <v>8</v>
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4588</v>
+        <v>6874</v>
       </c>
       <c r="C2" t="n">
-        <v>4513</v>
+        <v>7326</v>
       </c>
       <c r="D2" t="n">
-        <v>9100</v>
+        <v>9609</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3185</v>
+        <v>3458</v>
       </c>
       <c r="C2" t="n">
-        <v>3760</v>
+        <v>2646</v>
       </c>
       <c r="D2" t="n">
-        <v>14142</v>
+        <v>11322</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3457</v>
+        <v>3181</v>
       </c>
       <c r="C3" t="n">
-        <v>4162</v>
+        <v>3745</v>
       </c>
       <c r="D3" t="n">
-        <v>14507</v>
+        <v>14378</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3711</v>
+        <v>3666</v>
       </c>
       <c r="C4" t="n">
-        <v>6242</v>
+        <v>6496</v>
       </c>
       <c r="D4" t="n">
-        <v>13120</v>
+        <v>11348</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1622</v>
+        <v>1673</v>
       </c>
       <c r="C5" t="n">
-        <v>8599</v>
+        <v>8880</v>
       </c>
       <c r="D5" t="n">
-        <v>6714</v>
+        <v>5923</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>543</v>
+        <v>605</v>
       </c>
       <c r="C6" t="n">
-        <v>6147</v>
+        <v>6207</v>
       </c>
       <c r="D6" t="n">
-        <v>2139</v>
+        <v>2043</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>109</v>
+        <v>127</v>
       </c>
       <c r="C7" t="n">
-        <v>2687</v>
+        <v>2591</v>
       </c>
       <c r="D7" t="n">
-        <v>575</v>
+        <v>583</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="C8" t="n">
-        <v>1030</v>
+        <v>1098</v>
       </c>
       <c r="D8" t="n">
-        <v>305</v>
+        <v>301</v>
       </c>
     </row>
     <row r="9">
@@ -4302,10 +4302,10 @@
         <v>5</v>
       </c>
       <c r="C9" t="n">
-        <v>341</v>
+        <v>372</v>
       </c>
       <c r="D9" t="n">
-        <v>185</v>
+        <v>188</v>
       </c>
     </row>
     <row r="10">
@@ -4316,10 +4316,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="D10" t="n">
-        <v>134</v>
+        <v>136</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D11" t="n">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="12">
@@ -4347,7 +4347,7 @@
         <v>52</v>
       </c>
       <c r="D12" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="13">
@@ -4361,7 +4361,7 @@
         <v>38</v>
       </c>
       <c r="D13" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="14">
@@ -4372,10 +4372,10 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D14" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="15">
@@ -4386,7 +4386,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D15" t="n">
         <v>7</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6524</v>
+        <v>6985</v>
       </c>
       <c r="C2" t="n">
-        <v>5182</v>
+        <v>5070</v>
       </c>
       <c r="D2" t="n">
-        <v>8890</v>
+        <v>12238</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1950</v>
+        <v>2920</v>
       </c>
       <c r="C3" t="n">
-        <v>2310</v>
+        <v>3692</v>
       </c>
       <c r="D3" t="n">
-        <v>2168</v>
+        <v>2253</v>
       </c>
     </row>
     <row r="4">
@@ -4543,7 +4543,7 @@
         <v>79</v>
       </c>
       <c r="C4" t="n">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="D4" t="n">
         <v>1538</v>
@@ -4554,10 +4554,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="C5" t="n">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="D5" t="n">
         <v>1161</v>
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="C6" t="n">
         <v>459</v>
       </c>
       <c r="D6" t="n">
-        <v>808</v>
+        <v>816</v>
       </c>
     </row>
     <row r="7">
@@ -4588,7 +4588,7 @@
         <v>350</v>
       </c>
       <c r="D7" t="n">
-        <v>546</v>
+        <v>538</v>
       </c>
     </row>
     <row r="8">
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4395</v>
+        <v>5858</v>
       </c>
       <c r="C2" t="n">
-        <v>3597</v>
+        <v>4310</v>
       </c>
       <c r="D2" t="n">
-        <v>18267</v>
+        <v>27835</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3528</v>
+        <v>4068</v>
       </c>
       <c r="C3" t="n">
-        <v>3412</v>
+        <v>3856</v>
       </c>
       <c r="D3" t="n">
-        <v>3137</v>
+        <v>3764</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>880</v>
+        <v>1302</v>
       </c>
       <c r="C4" t="n">
-        <v>1418</v>
+        <v>2206</v>
       </c>
       <c r="D4" t="n">
-        <v>1618</v>
+        <v>1635</v>
       </c>
     </row>
     <row r="5">
@@ -4865,10 +4865,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C5" t="n">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="D5" t="n">
         <v>1186</v>
@@ -4879,13 +4879,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="C6" t="n">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="D6" t="n">
-        <v>864</v>
+        <v>870</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="C7" t="n">
         <v>409</v>
       </c>
       <c r="D7" t="n">
-        <v>589</v>
+        <v>584</v>
       </c>
     </row>
     <row r="8">
@@ -4910,10 +4910,10 @@
         <v>115</v>
       </c>
       <c r="C8" t="n">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="D8" t="n">
-        <v>441</v>
+        <v>439</v>
       </c>
     </row>
     <row r="9">
@@ -4924,7 +4924,7 @@
         <v>84</v>
       </c>
       <c r="C9" t="n">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="D9" t="n">
         <v>363</v>
@@ -4938,7 +4938,7 @@
         <v>63</v>
       </c>
       <c r="C10" t="n">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="D10" t="n">
         <v>352</v>
@@ -4949,7 +4949,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C11" t="n">
         <v>166</v>
@@ -4983,7 +4983,7 @@
         <v>103</v>
       </c>
       <c r="D13" t="n">
-        <v>170</v>
+        <v>172</v>
       </c>
     </row>
     <row r="14">
@@ -4997,7 +4997,7 @@
         <v>83</v>
       </c>
       <c r="D14" t="n">
-        <v>148</v>
+        <v>146</v>
       </c>
     </row>
     <row r="15">
@@ -5008,7 +5008,7 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D15" t="n">
         <v>120</v>
@@ -5022,7 +5022,7 @@
         <v>13</v>
       </c>
       <c r="C16" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D16" t="n">
         <v>98</v>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5739</v>
+        <v>5302</v>
       </c>
       <c r="C2" t="n">
-        <v>4566</v>
+        <v>2578</v>
       </c>
       <c r="D2" t="n">
-        <v>27578</v>
+        <v>27545</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3260</v>
+        <v>4063</v>
       </c>
       <c r="C3" t="n">
-        <v>3069</v>
+        <v>3552</v>
       </c>
       <c r="D3" t="n">
-        <v>5331</v>
+        <v>7344</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1892</v>
+        <v>2286</v>
       </c>
       <c r="C4" t="n">
-        <v>2504</v>
+        <v>3094</v>
       </c>
       <c r="D4" t="n">
-        <v>1844</v>
+        <v>1994</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>422</v>
+        <v>584</v>
       </c>
       <c r="C5" t="n">
-        <v>882</v>
+        <v>1302</v>
       </c>
       <c r="D5" t="n">
-        <v>1232</v>
+        <v>1220</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="C6" t="n">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="D6" t="n">
-        <v>910</v>
+        <v>915</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="C7" t="n">
-        <v>409</v>
+        <v>405</v>
       </c>
       <c r="D7" t="n">
-        <v>625</v>
+        <v>628</v>
       </c>
     </row>
     <row r="8">
@@ -5221,10 +5221,10 @@
         <v>125</v>
       </c>
       <c r="C8" t="n">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="D8" t="n">
-        <v>462</v>
+        <v>454</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C9" t="n">
         <v>268</v>
       </c>
       <c r="D9" t="n">
-        <v>372</v>
+        <v>371</v>
       </c>
     </row>
     <row r="10">
@@ -5246,10 +5246,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C10" t="n">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="D10" t="n">
         <v>346</v>
@@ -5263,7 +5263,7 @@
         <v>47</v>
       </c>
       <c r="C11" t="n">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="D11" t="n">
         <v>280</v>
@@ -5274,13 +5274,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C12" t="n">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D12" t="n">
-        <v>211</v>
+        <v>213</v>
       </c>
     </row>
     <row r="13">
@@ -5308,7 +5308,7 @@
         <v>91</v>
       </c>
       <c r="D14" t="n">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="15">
@@ -5319,10 +5319,10 @@
         <v>13</v>
       </c>
       <c r="C15" t="n">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D15" t="n">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="16">
@@ -5333,7 +5333,7 @@
         <v>12</v>
       </c>
       <c r="C16" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D16" t="n">
         <v>99</v>
@@ -5350,7 +5350,7 @@
         <v>68</v>
       </c>
       <c r="D17" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="18">
@@ -5361,10 +5361,10 @@
         <v>10</v>
       </c>
       <c r="C18" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D18" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="19">
@@ -5375,7 +5375,7 @@
         <v>10</v>
       </c>
       <c r="C19" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D19" t="n">
         <v>41</v>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5967</v>
+        <v>5143</v>
       </c>
       <c r="C2" t="n">
-        <v>7231</v>
+        <v>3335</v>
       </c>
       <c r="D2" t="n">
-        <v>31925</v>
+        <v>21744</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3629</v>
+        <v>3828</v>
       </c>
       <c r="C3" t="n">
-        <v>3348</v>
+        <v>2655</v>
       </c>
       <c r="D3" t="n">
-        <v>8337</v>
+        <v>9897</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2175</v>
+        <v>2698</v>
       </c>
       <c r="C4" t="n">
-        <v>2761</v>
+        <v>3275</v>
       </c>
       <c r="D4" t="n">
-        <v>2406</v>
+        <v>2909</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>959</v>
+        <v>1178</v>
       </c>
       <c r="C5" t="n">
-        <v>1720</v>
+        <v>2191</v>
       </c>
       <c r="D5" t="n">
-        <v>1306</v>
+        <v>1304</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>248</v>
+        <v>317</v>
       </c>
       <c r="C6" t="n">
-        <v>591</v>
+        <v>808</v>
       </c>
       <c r="D6" t="n">
-        <v>944</v>
+        <v>955</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="C7" t="n">
         <v>354</v>
       </c>
       <c r="D7" t="n">
-        <v>668</v>
+        <v>663</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C8" t="n">
-        <v>380</v>
+        <v>376</v>
       </c>
       <c r="D8" t="n">
-        <v>484</v>
+        <v>478</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="C9" t="n">
-        <v>305</v>
+        <v>310</v>
       </c>
       <c r="D9" t="n">
-        <v>378</v>
+        <v>376</v>
       </c>
     </row>
     <row r="10">
@@ -5557,10 +5557,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C10" t="n">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="D10" t="n">
         <v>346</v>
@@ -5574,10 +5574,10 @@
         <v>50</v>
       </c>
       <c r="C11" t="n">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="D11" t="n">
-        <v>284</v>
+        <v>286</v>
       </c>
     </row>
     <row r="12">
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C12" t="n">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D12" t="n">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="13">
@@ -5616,10 +5616,10 @@
         <v>15</v>
       </c>
       <c r="C14" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D14" t="n">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="15">
@@ -5630,10 +5630,10 @@
         <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D15" t="n">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="16">
@@ -5644,10 +5644,10 @@
         <v>11</v>
       </c>
       <c r="C16" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D16" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="17">
@@ -5658,7 +5658,7 @@
         <v>10</v>
       </c>
       <c r="C17" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D17" t="n">
         <v>79</v>
@@ -5672,10 +5672,10 @@
         <v>9</v>
       </c>
       <c r="C18" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D18" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="19">
@@ -5689,7 +5689,7 @@
         <v>62</v>
       </c>
       <c r="D19" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="20">
@@ -5700,7 +5700,7 @@
         <v>7</v>
       </c>
       <c r="C20" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D20" t="n">
         <v>24</v>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5930</v>
+        <v>5624</v>
       </c>
       <c r="C2" t="n">
-        <v>9222</v>
+        <v>5056</v>
       </c>
       <c r="D2" t="n">
-        <v>29798</v>
+        <v>19851</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3482</v>
+        <v>3253</v>
       </c>
       <c r="C3" t="n">
-        <v>4396</v>
+        <v>2459</v>
       </c>
       <c r="D3" t="n">
-        <v>10663</v>
+        <v>10350</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1800</v>
+        <v>2013</v>
       </c>
       <c r="C4" t="n">
-        <v>2534</v>
+        <v>2377</v>
       </c>
       <c r="D4" t="n">
-        <v>2961</v>
+        <v>3551</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>828</v>
+        <v>1008</v>
       </c>
       <c r="C5" t="n">
-        <v>1647</v>
+        <v>2018</v>
       </c>
       <c r="D5" t="n">
-        <v>1189</v>
+        <v>1262</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>286</v>
+        <v>357</v>
       </c>
       <c r="C6" t="n">
-        <v>789</v>
+        <v>1008</v>
       </c>
       <c r="D6" t="n">
-        <v>758</v>
+        <v>772</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>88</v>
+        <v>99</v>
       </c>
       <c r="C7" t="n">
-        <v>300</v>
+        <v>371</v>
       </c>
       <c r="D7" t="n">
-        <v>525</v>
+        <v>516</v>
       </c>
     </row>
     <row r="8">
@@ -5843,10 +5843,10 @@
         <v>58</v>
       </c>
       <c r="C8" t="n">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="D8" t="n">
-        <v>361</v>
+        <v>360</v>
       </c>
     </row>
     <row r="9">
@@ -5854,13 +5854,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C9" t="n">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="D9" t="n">
-        <v>273</v>
+        <v>268</v>
       </c>
     </row>
     <row r="10">
@@ -5871,7 +5871,7 @@
         <v>31</v>
       </c>
       <c r="C10" t="n">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="D10" t="n">
         <v>237</v>
@@ -5885,10 +5885,10 @@
         <v>21</v>
       </c>
       <c r="C11" t="n">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="D11" t="n">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="12">
@@ -5899,10 +5899,10 @@
         <v>14</v>
       </c>
       <c r="C12" t="n">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D12" t="n">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="13">
@@ -5913,7 +5913,7 @@
         <v>9</v>
       </c>
       <c r="C13" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D13" t="n">
         <v>116</v>
@@ -5927,7 +5927,7 @@
         <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D14" t="n">
         <v>97</v>
@@ -5958,7 +5958,7 @@
         <v>38</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="17">
@@ -5980,7 +5980,7 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C18" t="n">
         <v>33</v>
@@ -6000,7 +6000,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="20">
@@ -6025,7 +6025,7 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D21" t="n">
         <v>6</v>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5982</v>
+        <v>4964</v>
       </c>
       <c r="C2" t="n">
-        <v>7220</v>
+        <v>8042</v>
       </c>
       <c r="D2" t="n">
-        <v>24089</v>
+        <v>14941</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3926</v>
+        <v>3704</v>
       </c>
       <c r="C3" t="n">
-        <v>6272</v>
+        <v>3438</v>
       </c>
       <c r="D3" t="n">
-        <v>13228</v>
+        <v>11243</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2338</v>
+        <v>2319</v>
       </c>
       <c r="C4" t="n">
-        <v>3643</v>
+        <v>2377</v>
       </c>
       <c r="D4" t="n">
-        <v>4497</v>
+        <v>4878</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1180</v>
+        <v>1357</v>
       </c>
       <c r="C5" t="n">
-        <v>2149</v>
+        <v>2189</v>
       </c>
       <c r="D5" t="n">
-        <v>1498</v>
+        <v>1685</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>517</v>
+        <v>633</v>
       </c>
       <c r="C6" t="n">
-        <v>1281</v>
+        <v>1567</v>
       </c>
       <c r="D6" t="n">
-        <v>833</v>
+        <v>847</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>172</v>
+        <v>210</v>
       </c>
       <c r="C7" t="n">
-        <v>582</v>
+        <v>739</v>
       </c>
       <c r="D7" t="n">
-        <v>565</v>
+        <v>560</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="C8" t="n">
-        <v>266</v>
+        <v>305</v>
       </c>
       <c r="D8" t="n">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C9" t="n">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="D9" t="n">
-        <v>286</v>
+        <v>278</v>
       </c>
     </row>
     <row r="10">
@@ -6199,7 +6199,7 @@
         <v>132</v>
       </c>
       <c r="D11" t="n">
-        <v>196</v>
+        <v>199</v>
       </c>
     </row>
     <row r="12">
@@ -6210,10 +6210,10 @@
         <v>15</v>
       </c>
       <c r="C12" t="n">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="D12" t="n">
-        <v>154</v>
+        <v>152</v>
       </c>
     </row>
     <row r="13">
@@ -6241,7 +6241,7 @@
         <v>64</v>
       </c>
       <c r="D14" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="15">
@@ -6255,7 +6255,7 @@
         <v>50</v>
       </c>
       <c r="D15" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16">
@@ -6269,7 +6269,7 @@
         <v>40</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17">
@@ -6283,7 +6283,7 @@
         <v>36</v>
       </c>
       <c r="D17" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="18">
@@ -6297,7 +6297,7 @@
         <v>33</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="19">
@@ -6305,13 +6305,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C19" t="n">
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="20">
@@ -6336,7 +6336,7 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D21" t="n">
         <v>7</v>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5282</v>
+        <v>6228</v>
       </c>
       <c r="C2" t="n">
-        <v>4380</v>
+        <v>7087</v>
       </c>
       <c r="D2" t="n">
-        <v>28012</v>
+        <v>18859</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4065</v>
+        <v>3563</v>
       </c>
       <c r="C3" t="n">
-        <v>5874</v>
+        <v>5180</v>
       </c>
       <c r="D3" t="n">
-        <v>14013</v>
+        <v>11025</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2688</v>
+        <v>2585</v>
       </c>
       <c r="C4" t="n">
-        <v>5081</v>
+        <v>2915</v>
       </c>
       <c r="D4" t="n">
-        <v>5993</v>
+        <v>5904</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1553</v>
+        <v>1632</v>
       </c>
       <c r="C5" t="n">
-        <v>2915</v>
+        <v>2249</v>
       </c>
       <c r="D5" t="n">
-        <v>2028</v>
+        <v>2246</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>770</v>
+        <v>905</v>
       </c>
       <c r="C6" t="n">
-        <v>1740</v>
+        <v>1888</v>
       </c>
       <c r="D6" t="n">
-        <v>934</v>
+        <v>979</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>308</v>
+        <v>377</v>
       </c>
       <c r="C7" t="n">
-        <v>958</v>
+        <v>1184</v>
       </c>
       <c r="D7" t="n">
-        <v>609</v>
+        <v>607</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>105</v>
+        <v>123</v>
       </c>
       <c r="C8" t="n">
-        <v>430</v>
+        <v>530</v>
       </c>
       <c r="D8" t="n">
-        <v>412</v>
+        <v>411</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C9" t="n">
-        <v>236</v>
+        <v>255</v>
       </c>
       <c r="D9" t="n">
-        <v>296</v>
+        <v>290</v>
       </c>
     </row>
     <row r="10">
@@ -6493,10 +6493,10 @@
         <v>36</v>
       </c>
       <c r="C10" t="n">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="D10" t="n">
-        <v>245</v>
+        <v>243</v>
       </c>
     </row>
     <row r="11">
@@ -6510,7 +6510,7 @@
         <v>152</v>
       </c>
       <c r="D11" t="n">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="12">
@@ -6521,7 +6521,7 @@
         <v>16</v>
       </c>
       <c r="C12" t="n">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D12" t="n">
         <v>157</v>
@@ -6535,7 +6535,7 @@
         <v>10</v>
       </c>
       <c r="C13" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D13" t="n">
         <v>122</v>
@@ -6566,7 +6566,7 @@
         <v>55</v>
       </c>
       <c r="D15" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="16">
@@ -6580,7 +6580,7 @@
         <v>43</v>
       </c>
       <c r="D16" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="17">
@@ -6594,7 +6594,7 @@
         <v>37</v>
       </c>
       <c r="D17" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="18">
@@ -6622,7 +6622,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="20">
@@ -6630,7 +6630,7 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C20" t="n">
         <v>29</v>
@@ -6647,7 +6647,7 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D21" t="n">
         <v>8</v>

--- a/output/yearly_population_iteration_93_growth_param_0.5.xlsx
+++ b/output/yearly_population_iteration_93_growth_param_0.5.xlsx
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6964</v>
+        <v>1608</v>
       </c>
       <c r="C2" t="n">
-        <v>13313</v>
+        <v>3611</v>
       </c>
       <c r="D2" t="n">
-        <v>29117</v>
+        <v>13078</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3950</v>
+        <v>2337</v>
       </c>
       <c r="C3" t="n">
-        <v>5363</v>
+        <v>8687</v>
       </c>
       <c r="D3" t="n">
-        <v>11439</v>
+        <v>11866</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2638</v>
+        <v>1388</v>
       </c>
       <c r="C4" t="n">
-        <v>4044</v>
+        <v>9324</v>
       </c>
       <c r="D4" t="n">
-        <v>6601</v>
+        <v>5669</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1835</v>
+        <v>698</v>
       </c>
       <c r="C5" t="n">
-        <v>2553</v>
+        <v>5251</v>
       </c>
       <c r="D5" t="n">
-        <v>2844</v>
+        <v>1970</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1140</v>
+        <v>287</v>
       </c>
       <c r="C6" t="n">
-        <v>2050</v>
+        <v>2091</v>
       </c>
       <c r="D6" t="n">
-        <v>1184</v>
+        <v>755</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>565</v>
+        <v>102</v>
       </c>
       <c r="C7" t="n">
-        <v>1523</v>
+        <v>688</v>
       </c>
       <c r="D7" t="n">
-        <v>656</v>
+        <v>483</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>211</v>
+        <v>73</v>
       </c>
       <c r="C8" t="n">
-        <v>850</v>
+        <v>342</v>
       </c>
       <c r="D8" t="n">
-        <v>439</v>
+        <v>372</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>75</v>
+        <v>53</v>
       </c>
       <c r="C9" t="n">
-        <v>384</v>
+        <v>285</v>
       </c>
       <c r="D9" t="n">
-        <v>303</v>
+        <v>315</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="C10" t="n">
-        <v>218</v>
+        <v>211</v>
       </c>
       <c r="D10" t="n">
-        <v>247</v>
+        <v>270</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="C11" t="n">
-        <v>169</v>
+        <v>176</v>
       </c>
       <c r="D11" t="n">
-        <v>205</v>
+        <v>211</v>
       </c>
     </row>
     <row r="12">
@@ -920,13 +920,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>130</v>
+        <v>110</v>
       </c>
       <c r="D12" t="n">
-        <v>159</v>
+        <v>173</v>
       </c>
     </row>
     <row r="13">
@@ -934,13 +934,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C13" t="n">
-        <v>99</v>
+        <v>77</v>
       </c>
       <c r="D13" t="n">
-        <v>125</v>
+        <v>138</v>
       </c>
     </row>
     <row r="14">
@@ -948,13 +948,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>77</v>
+        <v>65</v>
       </c>
       <c r="D14" t="n">
-        <v>99</v>
+        <v>89</v>
       </c>
     </row>
     <row r="15">
@@ -965,10 +965,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D15" t="n">
-        <v>81</v>
+        <v>72</v>
       </c>
     </row>
     <row r="16">
@@ -976,13 +976,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C16" t="n">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>52</v>
       </c>
     </row>
     <row r="17">
@@ -990,13 +990,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C17" t="n">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>39</v>
       </c>
     </row>
     <row r="18">
@@ -1004,13 +1004,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C18" t="n">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>21</v>
       </c>
     </row>
     <row r="19">
@@ -1018,13 +1018,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>141</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20">
@@ -1035,10 +1035,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>99</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7122</v>
+        <v>938</v>
       </c>
       <c r="C2" t="n">
-        <v>7024</v>
+        <v>6824</v>
       </c>
       <c r="D2" t="n">
-        <v>25957</v>
+        <v>22184</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4313</v>
+        <v>1679</v>
       </c>
       <c r="C3" t="n">
-        <v>8009</v>
+        <v>5316</v>
       </c>
       <c r="D3" t="n">
-        <v>13197</v>
+        <v>11214</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2750</v>
+        <v>1589</v>
       </c>
       <c r="C4" t="n">
-        <v>4618</v>
+        <v>8787</v>
       </c>
       <c r="D4" t="n">
-        <v>7236</v>
+        <v>6626</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1944</v>
+        <v>895</v>
       </c>
       <c r="C5" t="n">
-        <v>3191</v>
+        <v>7303</v>
       </c>
       <c r="D5" t="n">
-        <v>3343</v>
+        <v>2549</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1337</v>
+        <v>427</v>
       </c>
       <c r="C6" t="n">
-        <v>2265</v>
+        <v>3636</v>
       </c>
       <c r="D6" t="n">
-        <v>1438</v>
+        <v>943</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>734</v>
+        <v>159</v>
       </c>
       <c r="C7" t="n">
-        <v>1750</v>
+        <v>1354</v>
       </c>
       <c r="D7" t="n">
-        <v>725</v>
+        <v>520</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>321</v>
+        <v>78</v>
       </c>
       <c r="C8" t="n">
-        <v>1153</v>
+        <v>497</v>
       </c>
       <c r="D8" t="n">
-        <v>468</v>
+        <v>388</v>
       </c>
     </row>
     <row r="9">
@@ -1189,10 +1189,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>117</v>
+        <v>56</v>
       </c>
       <c r="C9" t="n">
-        <v>581</v>
+        <v>313</v>
       </c>
       <c r="D9" t="n">
         <v>319</v>
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>48</v>
+        <v>29</v>
       </c>
       <c r="C10" t="n">
-        <v>287</v>
+        <v>242</v>
       </c>
       <c r="D10" t="n">
-        <v>249</v>
+        <v>275</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="C11" t="n">
-        <v>186</v>
+        <v>191</v>
       </c>
       <c r="D11" t="n">
-        <v>208</v>
+        <v>216</v>
       </c>
     </row>
     <row r="12">
@@ -1231,13 +1231,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>145</v>
+        <v>132</v>
       </c>
       <c r="D12" t="n">
-        <v>161</v>
+        <v>175</v>
       </c>
     </row>
     <row r="13">
@@ -1245,13 +1245,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C13" t="n">
-        <v>110</v>
+        <v>88</v>
       </c>
       <c r="D13" t="n">
-        <v>128</v>
+        <v>141</v>
       </c>
     </row>
     <row r="14">
@@ -1259,13 +1259,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C14" t="n">
-        <v>83</v>
+        <v>70</v>
       </c>
       <c r="D14" t="n">
-        <v>100</v>
+        <v>94</v>
       </c>
     </row>
     <row r="15">
@@ -1279,7 +1279,7 @@
         <v>65</v>
       </c>
       <c r="D15" t="n">
-        <v>82</v>
+        <v>71</v>
       </c>
     </row>
     <row r="16">
@@ -1290,10 +1290,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>51</v>
       </c>
     </row>
     <row r="17">
@@ -1301,13 +1301,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C17" t="n">
-        <v>40</v>
+        <v>57</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>37</v>
       </c>
     </row>
     <row r="18">
@@ -1315,13 +1315,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="C18" t="n">
-        <v>34</v>
+        <v>96</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>17</v>
       </c>
     </row>
     <row r="19">
@@ -1332,10 +1332,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>77</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20">
@@ -1346,10 +1346,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>106</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8002</v>
+        <v>506</v>
       </c>
       <c r="C2" t="n">
-        <v>7247</v>
+        <v>2871</v>
       </c>
       <c r="D2" t="n">
-        <v>25473</v>
+        <v>15120</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4483</v>
+        <v>1420</v>
       </c>
       <c r="C3" t="n">
-        <v>6695</v>
+        <v>5682</v>
       </c>
       <c r="D3" t="n">
-        <v>13964</v>
+        <v>12243</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2899</v>
+        <v>1743</v>
       </c>
       <c r="C4" t="n">
-        <v>6084</v>
+        <v>8199</v>
       </c>
       <c r="D4" t="n">
-        <v>7862</v>
+        <v>7227</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2045</v>
+        <v>899</v>
       </c>
       <c r="C5" t="n">
-        <v>3724</v>
+        <v>8623</v>
       </c>
       <c r="D5" t="n">
-        <v>3839</v>
+        <v>2848</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1455</v>
+        <v>336</v>
       </c>
       <c r="C6" t="n">
-        <v>2621</v>
+        <v>4600</v>
       </c>
       <c r="D6" t="n">
-        <v>1679</v>
+        <v>958</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>885</v>
+        <v>72</v>
       </c>
       <c r="C7" t="n">
-        <v>1971</v>
+        <v>1271</v>
       </c>
       <c r="D7" t="n">
-        <v>822</v>
+        <v>552</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>433</v>
+        <v>51</v>
       </c>
       <c r="C8" t="n">
-        <v>1386</v>
+        <v>477</v>
       </c>
       <c r="D8" t="n">
-        <v>493</v>
+        <v>436</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>174</v>
+        <v>26</v>
       </c>
       <c r="C9" t="n">
-        <v>810</v>
+        <v>237</v>
       </c>
       <c r="D9" t="n">
-        <v>336</v>
+        <v>366</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>65</v>
+        <v>14</v>
       </c>
       <c r="C10" t="n">
-        <v>396</v>
+        <v>187</v>
       </c>
       <c r="D10" t="n">
-        <v>252</v>
+        <v>211</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>32</v>
+        <v>9</v>
       </c>
       <c r="C11" t="n">
-        <v>223</v>
+        <v>129</v>
       </c>
       <c r="D11" t="n">
-        <v>211</v>
+        <v>171</v>
       </c>
     </row>
     <row r="12">
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="C12" t="n">
-        <v>157</v>
+        <v>86</v>
       </c>
       <c r="D12" t="n">
-        <v>163</v>
+        <v>138</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="C13" t="n">
-        <v>121</v>
+        <v>68</v>
       </c>
       <c r="D13" t="n">
-        <v>130</v>
+        <v>92</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>90</v>
+        <v>63</v>
       </c>
       <c r="D14" t="n">
-        <v>101</v>
+        <v>69</v>
       </c>
     </row>
     <row r="15">
@@ -1584,13 +1584,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="D15" t="n">
-        <v>83</v>
+        <v>49</v>
       </c>
     </row>
     <row r="16">
@@ -1598,13 +1598,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C16" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>36</v>
       </c>
     </row>
     <row r="17">
@@ -1612,13 +1612,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="C17" t="n">
-        <v>42</v>
+        <v>94</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>16</v>
       </c>
     </row>
     <row r="18">
@@ -1626,13 +1626,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>35</v>
+        <v>75</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -1643,10 +1643,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1657,10 +1657,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>112</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7291</v>
+        <v>530</v>
       </c>
       <c r="C2" t="n">
-        <v>4812</v>
+        <v>3784</v>
       </c>
       <c r="D2" t="n">
-        <v>20710</v>
+        <v>12661</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5410</v>
+        <v>871</v>
       </c>
       <c r="C3" t="n">
-        <v>9749</v>
+        <v>3772</v>
       </c>
       <c r="D3" t="n">
-        <v>15412</v>
+        <v>11814</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1889</v>
+        <v>1426</v>
       </c>
       <c r="C4" t="n">
-        <v>7079</v>
+        <v>6802</v>
       </c>
       <c r="D4" t="n">
-        <v>7824</v>
+        <v>7874</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1344</v>
+        <v>1119</v>
       </c>
       <c r="C5" t="n">
-        <v>2568</v>
+        <v>8318</v>
       </c>
       <c r="D5" t="n">
-        <v>2714</v>
+        <v>3476</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>817</v>
+        <v>508</v>
       </c>
       <c r="C6" t="n">
-        <v>1931</v>
+        <v>6497</v>
       </c>
       <c r="D6" t="n">
-        <v>805</v>
+        <v>1244</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>400</v>
+        <v>143</v>
       </c>
       <c r="C7" t="n">
-        <v>1358</v>
+        <v>2730</v>
       </c>
       <c r="D7" t="n">
-        <v>483</v>
+        <v>607</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>160</v>
+        <v>54</v>
       </c>
       <c r="C8" t="n">
-        <v>793</v>
+        <v>797</v>
       </c>
       <c r="D8" t="n">
-        <v>329</v>
+        <v>449</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="C9" t="n">
-        <v>388</v>
+        <v>328</v>
       </c>
       <c r="D9" t="n">
-        <v>246</v>
+        <v>372</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="C10" t="n">
-        <v>218</v>
+        <v>209</v>
       </c>
       <c r="D10" t="n">
-        <v>206</v>
+        <v>225</v>
       </c>
     </row>
     <row r="11">
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="C11" t="n">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="D11" t="n">
-        <v>159</v>
+        <v>175</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="C12" t="n">
-        <v>118</v>
+        <v>99</v>
       </c>
       <c r="D12" t="n">
-        <v>127</v>
+        <v>142</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C13" t="n">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="D13" t="n">
-        <v>98</v>
+        <v>92</v>
       </c>
     </row>
     <row r="14">
@@ -1881,13 +1881,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C14" t="n">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="D14" t="n">
-        <v>81</v>
+        <v>68</v>
       </c>
     </row>
     <row r="15">
@@ -1898,10 +1898,10 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>52</v>
+        <v>67</v>
       </c>
       <c r="D15" t="n">
-        <v>63</v>
+        <v>48</v>
       </c>
     </row>
     <row r="16">
@@ -1909,13 +1909,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="C16" t="n">
-        <v>41</v>
+        <v>91</v>
       </c>
       <c r="D16" t="n">
-        <v>50</v>
+        <v>31</v>
       </c>
     </row>
     <row r="17">
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>34</v>
+        <v>100</v>
       </c>
       <c r="D17" t="n">
-        <v>38</v>
+        <v>10</v>
       </c>
     </row>
     <row r="18">
@@ -1940,10 +1940,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="D18" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1954,10 +1954,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1965,13 +1965,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>112</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4482</v>
+        <v>354</v>
       </c>
       <c r="C2" t="n">
-        <v>2282</v>
+        <v>2678</v>
       </c>
       <c r="D2" t="n">
-        <v>14291</v>
+        <v>9106</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5399</v>
+        <v>655</v>
       </c>
       <c r="C3" t="n">
-        <v>6719</v>
+        <v>3432</v>
       </c>
       <c r="D3" t="n">
-        <v>15410</v>
+        <v>11362</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2834</v>
+        <v>1151</v>
       </c>
       <c r="C4" t="n">
-        <v>8417</v>
+        <v>5489</v>
       </c>
       <c r="D4" t="n">
-        <v>8826</v>
+        <v>8277</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1490</v>
+        <v>1184</v>
       </c>
       <c r="C5" t="n">
-        <v>4586</v>
+        <v>7853</v>
       </c>
       <c r="D5" t="n">
-        <v>3396</v>
+        <v>3985</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>978</v>
+        <v>622</v>
       </c>
       <c r="C6" t="n">
-        <v>2280</v>
+        <v>7395</v>
       </c>
       <c r="D6" t="n">
-        <v>1002</v>
+        <v>1467</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>379</v>
+        <v>156</v>
       </c>
       <c r="C7" t="n">
-        <v>1626</v>
+        <v>3986</v>
       </c>
       <c r="D7" t="n">
-        <v>525</v>
+        <v>677</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>134</v>
+        <v>51</v>
       </c>
       <c r="C8" t="n">
-        <v>1013</v>
+        <v>1256</v>
       </c>
       <c r="D8" t="n">
-        <v>343</v>
+        <v>472</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>48</v>
+        <v>25</v>
       </c>
       <c r="C9" t="n">
-        <v>453</v>
+        <v>419</v>
       </c>
       <c r="D9" t="n">
-        <v>258</v>
+        <v>372</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="C10" t="n">
-        <v>236</v>
+        <v>227</v>
       </c>
       <c r="D10" t="n">
-        <v>212</v>
+        <v>231</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C11" t="n">
-        <v>171</v>
+        <v>153</v>
       </c>
       <c r="D11" t="n">
-        <v>167</v>
+        <v>183</v>
       </c>
     </row>
     <row r="12">
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C12" t="n">
-        <v>98</v>
+        <v>107</v>
       </c>
       <c r="D12" t="n">
-        <v>132</v>
+        <v>136</v>
       </c>
     </row>
     <row r="13">
@@ -2178,13 +2178,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="D13" t="n">
-        <v>101</v>
+        <v>93</v>
       </c>
     </row>
     <row r="14">
@@ -2195,10 +2195,10 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="D14" t="n">
-        <v>61</v>
+        <v>53</v>
       </c>
     </row>
     <row r="15">
@@ -2206,13 +2206,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="C15" t="n">
-        <v>40</v>
+        <v>89</v>
       </c>
       <c r="D15" t="n">
-        <v>49</v>
+        <v>30</v>
       </c>
     </row>
     <row r="16">
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>33</v>
+        <v>98</v>
       </c>
       <c r="D16" t="n">
-        <v>37</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17">
@@ -2237,10 +2237,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2262,13 +2262,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>109</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4566</v>
+        <v>951</v>
       </c>
       <c r="C2" t="n">
-        <v>8169</v>
+        <v>12169</v>
       </c>
       <c r="D2" t="n">
-        <v>22445</v>
+        <v>12870</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4199</v>
+        <v>450</v>
       </c>
       <c r="C3" t="n">
-        <v>4017</v>
+        <v>2730</v>
       </c>
       <c r="D3" t="n">
-        <v>14188</v>
+        <v>10400</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3426</v>
+        <v>841</v>
       </c>
       <c r="C4" t="n">
-        <v>7377</v>
+        <v>4407</v>
       </c>
       <c r="D4" t="n">
-        <v>9695</v>
+        <v>8419</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1833</v>
+        <v>1073</v>
       </c>
       <c r="C5" t="n">
-        <v>6366</v>
+        <v>6698</v>
       </c>
       <c r="D5" t="n">
-        <v>4178</v>
+        <v>4523</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1105</v>
+        <v>773</v>
       </c>
       <c r="C6" t="n">
-        <v>3363</v>
+        <v>7520</v>
       </c>
       <c r="D6" t="n">
-        <v>1356</v>
+        <v>1810</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>552</v>
+        <v>287</v>
       </c>
       <c r="C7" t="n">
-        <v>1936</v>
+        <v>5426</v>
       </c>
       <c r="D7" t="n">
-        <v>589</v>
+        <v>778</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>196</v>
+        <v>76</v>
       </c>
       <c r="C8" t="n">
-        <v>1280</v>
+        <v>2298</v>
       </c>
       <c r="D8" t="n">
-        <v>364</v>
+        <v>493</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>67</v>
+        <v>29</v>
       </c>
       <c r="C9" t="n">
-        <v>676</v>
+        <v>726</v>
       </c>
       <c r="D9" t="n">
-        <v>268</v>
+        <v>383</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="C10" t="n">
-        <v>319</v>
+        <v>295</v>
       </c>
       <c r="D10" t="n">
-        <v>216</v>
+        <v>242</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C11" t="n">
-        <v>195</v>
+        <v>177</v>
       </c>
       <c r="D11" t="n">
-        <v>169</v>
+        <v>187</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C12" t="n">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D12" t="n">
-        <v>135</v>
+        <v>139</v>
       </c>
     </row>
     <row r="13">
@@ -2492,10 +2492,10 @@
         <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="D13" t="n">
-        <v>102</v>
+        <v>95</v>
       </c>
     </row>
     <row r="14">
@@ -2503,13 +2503,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>54</v>
+        <v>67</v>
       </c>
       <c r="D14" t="n">
-        <v>64</v>
+        <v>55</v>
       </c>
     </row>
     <row r="15">
@@ -2517,13 +2517,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="C15" t="n">
-        <v>44</v>
+        <v>92</v>
       </c>
       <c r="D15" t="n">
-        <v>48</v>
+        <v>29</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>36</v>
+        <v>98</v>
       </c>
       <c r="D16" t="n">
-        <v>36</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17">
@@ -2548,10 +2548,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2559,13 +2559,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2670</v>
+        <v>646</v>
       </c>
       <c r="C2" t="n">
-        <v>3696</v>
+        <v>6523</v>
       </c>
       <c r="D2" t="n">
-        <v>15455</v>
+        <v>9369</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4173</v>
+        <v>741</v>
       </c>
       <c r="C3" t="n">
-        <v>5343</v>
+        <v>5440</v>
       </c>
       <c r="D3" t="n">
-        <v>14772</v>
+        <v>11395</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3777</v>
+        <v>1404</v>
       </c>
       <c r="C4" t="n">
-        <v>6770</v>
+        <v>6424</v>
       </c>
       <c r="D4" t="n">
-        <v>10296</v>
+        <v>8595</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1923</v>
+        <v>773</v>
       </c>
       <c r="C5" t="n">
-        <v>7515</v>
+        <v>10230</v>
       </c>
       <c r="D5" t="n">
-        <v>4516</v>
+        <v>4212</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>979</v>
+        <v>265</v>
       </c>
       <c r="C6" t="n">
-        <v>4160</v>
+        <v>7086</v>
       </c>
       <c r="D6" t="n">
-        <v>1334</v>
+        <v>1560</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>181</v>
+        <v>70</v>
       </c>
       <c r="C7" t="n">
-        <v>2168</v>
+        <v>2252</v>
       </c>
       <c r="D7" t="n">
-        <v>592</v>
+        <v>589</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>61</v>
+        <v>26</v>
       </c>
       <c r="C8" t="n">
-        <v>1076</v>
+        <v>711</v>
       </c>
       <c r="D8" t="n">
-        <v>384</v>
+        <v>375</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="C9" t="n">
-        <v>312</v>
+        <v>289</v>
       </c>
       <c r="D9" t="n">
-        <v>293</v>
+        <v>237</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="C10" t="n">
-        <v>191</v>
+        <v>173</v>
       </c>
       <c r="D10" t="n">
-        <v>165</v>
+        <v>183</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C11" t="n">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D11" t="n">
-        <v>132</v>
+        <v>136</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="D12" t="n">
-        <v>99</v>
+        <v>93</v>
       </c>
     </row>
     <row r="13">
@@ -2800,13 +2800,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>52</v>
+        <v>65</v>
       </c>
       <c r="D13" t="n">
-        <v>62</v>
+        <v>53</v>
       </c>
     </row>
     <row r="14">
@@ -2814,13 +2814,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>43</v>
+        <v>90</v>
       </c>
       <c r="D14" t="n">
-        <v>47</v>
+        <v>28</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>35</v>
+        <v>96</v>
       </c>
       <c r="D15" t="n">
-        <v>35</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16">
@@ -2845,10 +2845,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -2856,13 +2856,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>63</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3381</v>
+        <v>318</v>
       </c>
       <c r="C2" t="n">
-        <v>4894</v>
+        <v>3362</v>
       </c>
       <c r="D2" t="n">
-        <v>19562</v>
+        <v>7274</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3016</v>
+        <v>590</v>
       </c>
       <c r="C3" t="n">
-        <v>4050</v>
+        <v>5257</v>
       </c>
       <c r="D3" t="n">
-        <v>13995</v>
+        <v>10286</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3485</v>
+        <v>926</v>
       </c>
       <c r="C4" t="n">
-        <v>5930</v>
+        <v>5623</v>
       </c>
       <c r="D4" t="n">
-        <v>10713</v>
+        <v>8449</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2381</v>
+        <v>734</v>
       </c>
       <c r="C5" t="n">
-        <v>7080</v>
+        <v>7442</v>
       </c>
       <c r="D5" t="n">
-        <v>5266</v>
+        <v>4360</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1237</v>
+        <v>265</v>
       </c>
       <c r="C6" t="n">
-        <v>5683</v>
+        <v>6970</v>
       </c>
       <c r="D6" t="n">
-        <v>1787</v>
+        <v>1629</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>382</v>
+        <v>59</v>
       </c>
       <c r="C7" t="n">
-        <v>3008</v>
+        <v>3052</v>
       </c>
       <c r="D7" t="n">
-        <v>680</v>
+        <v>569</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>85</v>
+        <v>13</v>
       </c>
       <c r="C8" t="n">
-        <v>1524</v>
+        <v>836</v>
       </c>
       <c r="D8" t="n">
-        <v>408</v>
+        <v>323</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="C9" t="n">
-        <v>572</v>
+        <v>268</v>
       </c>
       <c r="D9" t="n">
-        <v>301</v>
+        <v>188</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>233</v>
+        <v>123</v>
       </c>
       <c r="D10" t="n">
-        <v>176</v>
+        <v>140</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>140</v>
+        <v>75</v>
       </c>
       <c r="D11" t="n">
-        <v>136</v>
+        <v>99</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>84</v>
+        <v>53</v>
       </c>
       <c r="D12" t="n">
-        <v>101</v>
+        <v>62</v>
       </c>
     </row>
     <row r="13">
@@ -3111,13 +3111,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="D13" t="n">
-        <v>62</v>
+        <v>31</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="D14" t="n">
-        <v>47</v>
+        <v>9</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3153,13 +3153,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>57</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3184,10 +3184,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2578</v>
+        <v>332</v>
       </c>
       <c r="C2" t="n">
-        <v>2743</v>
+        <v>10894</v>
       </c>
       <c r="D2" t="n">
-        <v>14259</v>
+        <v>7212</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2748</v>
+        <v>388</v>
       </c>
       <c r="C3" t="n">
-        <v>4017</v>
+        <v>3703</v>
       </c>
       <c r="D3" t="n">
-        <v>14058</v>
+        <v>9104</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3078</v>
+        <v>678</v>
       </c>
       <c r="C4" t="n">
-        <v>5183</v>
+        <v>5305</v>
       </c>
       <c r="D4" t="n">
-        <v>10931</v>
+        <v>8527</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2604</v>
+        <v>747</v>
       </c>
       <c r="C5" t="n">
-        <v>6706</v>
+        <v>6398</v>
       </c>
       <c r="D5" t="n">
-        <v>5834</v>
+        <v>4934</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1452</v>
+        <v>429</v>
       </c>
       <c r="C6" t="n">
-        <v>6432</v>
+        <v>7130</v>
       </c>
       <c r="D6" t="n">
-        <v>2101</v>
+        <v>2052</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>370</v>
+        <v>128</v>
       </c>
       <c r="C7" t="n">
-        <v>3865</v>
+        <v>5000</v>
       </c>
       <c r="D7" t="n">
-        <v>766</v>
+        <v>729</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>70</v>
+        <v>27</v>
       </c>
       <c r="C8" t="n">
-        <v>1951</v>
+        <v>1864</v>
       </c>
       <c r="D8" t="n">
-        <v>431</v>
+        <v>355</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="C9" t="n">
-        <v>679</v>
+        <v>515</v>
       </c>
       <c r="D9" t="n">
-        <v>297</v>
+        <v>204</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>241</v>
+        <v>182</v>
       </c>
       <c r="D10" t="n">
-        <v>181</v>
+        <v>144</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>137</v>
+        <v>94</v>
       </c>
       <c r="D11" t="n">
-        <v>138</v>
+        <v>103</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>83</v>
+        <v>61</v>
       </c>
       <c r="D12" t="n">
-        <v>94</v>
+        <v>65</v>
       </c>
     </row>
     <row r="13">
@@ -3422,13 +3422,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>45</v>
+        <v>56</v>
       </c>
       <c r="D13" t="n">
-        <v>63</v>
+        <v>33</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>37</v>
+        <v>55</v>
       </c>
       <c r="D14" t="n">
-        <v>36</v>
+        <v>10</v>
       </c>
     </row>
     <row r="15">
@@ -3450,13 +3450,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>55</v>
+        <v>10</v>
       </c>
       <c r="D15" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>73</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3481,10 +3481,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4889</v>
+        <v>507</v>
       </c>
       <c r="C2" t="n">
-        <v>4724</v>
+        <v>11064</v>
       </c>
       <c r="D2" t="n">
-        <v>15382</v>
+        <v>6438</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2258</v>
+        <v>302</v>
       </c>
       <c r="C3" t="n">
-        <v>3091</v>
+        <v>6238</v>
       </c>
       <c r="D3" t="n">
-        <v>13296</v>
+        <v>8205</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2570</v>
+        <v>482</v>
       </c>
       <c r="C4" t="n">
-        <v>4560</v>
+        <v>4394</v>
       </c>
       <c r="D4" t="n">
-        <v>10944</v>
+        <v>8367</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2554</v>
+        <v>650</v>
       </c>
       <c r="C5" t="n">
-        <v>5923</v>
+        <v>5740</v>
       </c>
       <c r="D5" t="n">
-        <v>6390</v>
+        <v>5370</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1709</v>
+        <v>521</v>
       </c>
       <c r="C6" t="n">
-        <v>6485</v>
+        <v>6651</v>
       </c>
       <c r="D6" t="n">
-        <v>2575</v>
+        <v>2447</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>655</v>
+        <v>226</v>
       </c>
       <c r="C7" t="n">
-        <v>4907</v>
+        <v>5979</v>
       </c>
       <c r="D7" t="n">
-        <v>928</v>
+        <v>929</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>138</v>
+        <v>59</v>
       </c>
       <c r="C8" t="n">
-        <v>2644</v>
+        <v>3246</v>
       </c>
       <c r="D8" t="n">
-        <v>465</v>
+        <v>406</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="C9" t="n">
-        <v>1121</v>
+        <v>1083</v>
       </c>
       <c r="D9" t="n">
-        <v>308</v>
+        <v>220</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C10" t="n">
-        <v>380</v>
+        <v>315</v>
       </c>
       <c r="D10" t="n">
-        <v>192</v>
+        <v>150</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>169</v>
+        <v>127</v>
       </c>
       <c r="D11" t="n">
-        <v>139</v>
+        <v>107</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>97</v>
+        <v>72</v>
       </c>
       <c r="D12" t="n">
-        <v>96</v>
+        <v>68</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="D13" t="n">
-        <v>64</v>
+        <v>35</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>39</v>
+        <v>55</v>
       </c>
       <c r="D14" t="n">
-        <v>37</v>
+        <v>12</v>
       </c>
     </row>
     <row r="15">
@@ -3761,13 +3761,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>57</v>
+        <v>23</v>
       </c>
       <c r="D15" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>72</v>
+        <v>2</v>
       </c>
       <c r="D16" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6874</v>
+        <v>3965</v>
       </c>
       <c r="C2" t="n">
-        <v>7326</v>
+        <v>7942</v>
       </c>
       <c r="D2" t="n">
-        <v>9609</v>
+        <v>16568</v>
       </c>
     </row>
     <row r="3">
@@ -3904,13 +3904,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>843</v>
+        <v>855</v>
       </c>
     </row>
     <row r="4">
@@ -3918,13 +3918,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>175</v>
+        <v>205</v>
       </c>
       <c r="C4" t="n">
-        <v>313</v>
+        <v>344</v>
       </c>
       <c r="D4" t="n">
-        <v>1805</v>
+        <v>1906</v>
       </c>
     </row>
     <row r="5">
@@ -3932,13 +3932,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>249</v>
+        <v>314</v>
       </c>
       <c r="C5" t="n">
-        <v>515</v>
+        <v>586</v>
       </c>
       <c r="D5" t="n">
-        <v>1038</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="6">
@@ -3946,13 +3946,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>182</v>
+        <v>255</v>
       </c>
       <c r="C6" t="n">
-        <v>395</v>
+        <v>488</v>
       </c>
       <c r="D6" t="n">
-        <v>777</v>
+        <v>898</v>
       </c>
     </row>
     <row r="7">
@@ -3960,13 +3960,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>129</v>
+        <v>202</v>
       </c>
       <c r="C7" t="n">
-        <v>293</v>
+        <v>388</v>
       </c>
       <c r="D7" t="n">
-        <v>496</v>
+        <v>596</v>
       </c>
     </row>
     <row r="8">
@@ -3974,13 +3974,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>99</v>
+        <v>171</v>
       </c>
       <c r="C8" t="n">
-        <v>222</v>
+        <v>307</v>
       </c>
       <c r="D8" t="n">
-        <v>420</v>
+        <v>531</v>
       </c>
     </row>
     <row r="9">
@@ -3988,13 +3988,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>75</v>
+        <v>136</v>
       </c>
       <c r="C9" t="n">
-        <v>187</v>
+        <v>277</v>
       </c>
       <c r="D9" t="n">
-        <v>349</v>
+        <v>445</v>
       </c>
     </row>
     <row r="10">
@@ -4002,13 +4002,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>53</v>
+        <v>105</v>
       </c>
       <c r="C10" t="n">
-        <v>173</v>
+        <v>265</v>
       </c>
       <c r="D10" t="n">
-        <v>362</v>
+        <v>485</v>
       </c>
     </row>
     <row r="11">
@@ -4016,13 +4016,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>34</v>
+        <v>71</v>
       </c>
       <c r="C11" t="n">
-        <v>137</v>
+        <v>215</v>
       </c>
       <c r="D11" t="n">
-        <v>245</v>
+        <v>327</v>
       </c>
     </row>
     <row r="12">
@@ -4030,13 +4030,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="C12" t="n">
-        <v>104</v>
+        <v>169</v>
       </c>
       <c r="D12" t="n">
-        <v>196</v>
+        <v>274</v>
       </c>
     </row>
     <row r="13">
@@ -4044,13 +4044,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="C13" t="n">
-        <v>84</v>
+        <v>142</v>
       </c>
       <c r="D13" t="n">
-        <v>168</v>
+        <v>234</v>
       </c>
     </row>
     <row r="14">
@@ -4058,13 +4058,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="C14" t="n">
-        <v>75</v>
+        <v>128</v>
       </c>
       <c r="D14" t="n">
-        <v>145</v>
+        <v>207</v>
       </c>
     </row>
     <row r="15">
@@ -4072,13 +4072,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="C15" t="n">
-        <v>72</v>
+        <v>127</v>
       </c>
       <c r="D15" t="n">
-        <v>117</v>
+        <v>171</v>
       </c>
     </row>
     <row r="16">
@@ -4086,13 +4086,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>124</v>
       </c>
       <c r="D16" t="n">
-        <v>97</v>
+        <v>140</v>
       </c>
     </row>
     <row r="17">
@@ -4100,13 +4100,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="C17" t="n">
-        <v>66</v>
+        <v>119</v>
       </c>
       <c r="D17" t="n">
-        <v>76</v>
+        <v>114</v>
       </c>
     </row>
     <row r="18">
@@ -4114,13 +4114,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="C18" t="n">
-        <v>63</v>
+        <v>116</v>
       </c>
       <c r="D18" t="n">
-        <v>57</v>
+        <v>85</v>
       </c>
     </row>
     <row r="19">
@@ -4128,13 +4128,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="C19" t="n">
-        <v>60</v>
+        <v>111</v>
       </c>
       <c r="D19" t="n">
-        <v>38</v>
+        <v>58</v>
       </c>
     </row>
     <row r="20">
@@ -4142,13 +4142,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>109</v>
       </c>
       <c r="D20" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
     </row>
     <row r="21">
@@ -4156,10 +4156,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="C21" t="n">
-        <v>72</v>
+        <v>131</v>
       </c>
       <c r="D21" t="n">
         <v>1</v>
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3458</v>
+        <v>888</v>
       </c>
       <c r="C2" t="n">
-        <v>2646</v>
+        <v>22128</v>
       </c>
       <c r="D2" t="n">
-        <v>11322</v>
+        <v>7811</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3181</v>
+        <v>315</v>
       </c>
       <c r="C3" t="n">
-        <v>3745</v>
+        <v>7333</v>
       </c>
       <c r="D3" t="n">
-        <v>14378</v>
+        <v>7440</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3666</v>
+        <v>354</v>
       </c>
       <c r="C4" t="n">
-        <v>6496</v>
+        <v>5134</v>
       </c>
       <c r="D4" t="n">
-        <v>11348</v>
+        <v>8087</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1673</v>
+        <v>540</v>
       </c>
       <c r="C5" t="n">
-        <v>8880</v>
+        <v>4984</v>
       </c>
       <c r="D5" t="n">
-        <v>5923</v>
+        <v>5586</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>605</v>
+        <v>529</v>
       </c>
       <c r="C6" t="n">
-        <v>6207</v>
+        <v>6205</v>
       </c>
       <c r="D6" t="n">
-        <v>2043</v>
+        <v>2835</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>127</v>
+        <v>308</v>
       </c>
       <c r="C7" t="n">
-        <v>2591</v>
+        <v>6194</v>
       </c>
       <c r="D7" t="n">
-        <v>583</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>26</v>
+        <v>105</v>
       </c>
       <c r="C8" t="n">
-        <v>1098</v>
+        <v>4342</v>
       </c>
       <c r="D8" t="n">
-        <v>301</v>
+        <v>473</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="C9" t="n">
-        <v>372</v>
+        <v>1909</v>
       </c>
       <c r="D9" t="n">
-        <v>188</v>
+        <v>239</v>
       </c>
     </row>
     <row r="10">
@@ -4313,13 +4313,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C10" t="n">
-        <v>165</v>
+        <v>590</v>
       </c>
       <c r="D10" t="n">
-        <v>136</v>
+        <v>157</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>95</v>
+        <v>193</v>
       </c>
       <c r="D11" t="n">
-        <v>94</v>
+        <v>110</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>52</v>
+        <v>90</v>
       </c>
       <c r="D12" t="n">
-        <v>62</v>
+        <v>70</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
+        <v>61</v>
+      </c>
+      <c r="D13" t="n">
         <v>38</v>
-      </c>
-      <c r="D13" t="n">
-        <v>36</v>
       </c>
     </row>
     <row r="14">
@@ -4369,13 +4369,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
         <v>55</v>
       </c>
       <c r="D14" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="15">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>70</v>
+        <v>32</v>
       </c>
       <c r="D15" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -4400,7 +4400,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6985</v>
+        <v>5490</v>
       </c>
       <c r="C2" t="n">
-        <v>5070</v>
+        <v>13633</v>
       </c>
       <c r="D2" t="n">
-        <v>12238</v>
+        <v>21553</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2920</v>
+        <v>1311</v>
       </c>
       <c r="C3" t="n">
-        <v>3692</v>
+        <v>3136</v>
       </c>
       <c r="D3" t="n">
-        <v>2253</v>
+        <v>2869</v>
       </c>
     </row>
     <row r="4">
@@ -4540,13 +4540,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="C4" t="n">
-        <v>117</v>
+        <v>134</v>
       </c>
       <c r="D4" t="n">
-        <v>1538</v>
+        <v>1446</v>
       </c>
     </row>
     <row r="5">
@@ -4554,13 +4554,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>193</v>
+        <v>148</v>
       </c>
       <c r="C5" t="n">
-        <v>381</v>
+        <v>334</v>
       </c>
       <c r="D5" t="n">
-        <v>1161</v>
+        <v>986</v>
       </c>
     </row>
     <row r="6">
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>200</v>
+        <v>143</v>
       </c>
       <c r="C6" t="n">
-        <v>459</v>
+        <v>360</v>
       </c>
       <c r="D6" t="n">
-        <v>816</v>
+        <v>712</v>
       </c>
     </row>
     <row r="7">
@@ -4582,13 +4582,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>145</v>
+        <v>102</v>
       </c>
       <c r="C7" t="n">
-        <v>350</v>
+        <v>277</v>
       </c>
       <c r="D7" t="n">
-        <v>538</v>
+        <v>466</v>
       </c>
     </row>
     <row r="8">
@@ -4596,13 +4596,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>105</v>
+        <v>78</v>
       </c>
       <c r="C8" t="n">
-        <v>260</v>
+        <v>206</v>
       </c>
       <c r="D8" t="n">
-        <v>429</v>
+        <v>384</v>
       </c>
     </row>
     <row r="9">
@@ -4610,13 +4610,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="C9" t="n">
-        <v>205</v>
+        <v>169</v>
       </c>
       <c r="D9" t="n">
-        <v>354</v>
+        <v>313</v>
       </c>
     </row>
     <row r="10">
@@ -4624,13 +4624,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>58</v>
+        <v>44</v>
       </c>
       <c r="C10" t="n">
-        <v>180</v>
+        <v>153</v>
       </c>
       <c r="D10" t="n">
-        <v>356</v>
+        <v>324</v>
       </c>
     </row>
     <row r="11">
@@ -4638,13 +4638,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="C11" t="n">
-        <v>154</v>
+        <v>128</v>
       </c>
       <c r="D11" t="n">
-        <v>261</v>
+        <v>231</v>
       </c>
     </row>
     <row r="12">
@@ -4652,13 +4652,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="C12" t="n">
-        <v>119</v>
+        <v>100</v>
       </c>
       <c r="D12" t="n">
-        <v>199</v>
+        <v>182</v>
       </c>
     </row>
     <row r="13">
@@ -4666,13 +4666,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C13" t="n">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="D13" t="n">
-        <v>170</v>
+        <v>154</v>
       </c>
     </row>
     <row r="14">
@@ -4680,13 +4680,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="D14" t="n">
-        <v>146</v>
+        <v>133</v>
       </c>
     </row>
     <row r="15">
@@ -4694,13 +4694,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="D15" t="n">
-        <v>118</v>
+        <v>111</v>
       </c>
     </row>
     <row r="16">
@@ -4708,13 +4708,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="D16" t="n">
-        <v>98</v>
+        <v>89</v>
       </c>
     </row>
     <row r="17">
@@ -4722,13 +4722,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C17" t="n">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="D17" t="n">
-        <v>77</v>
+        <v>73</v>
       </c>
     </row>
     <row r="18">
@@ -4736,13 +4736,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C18" t="n">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="D18" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
     </row>
     <row r="19">
@@ -4750,13 +4750,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="D19" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
     </row>
     <row r="20">
@@ -4767,10 +4767,10 @@
         <v>10</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="21">
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C21" t="n">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="D21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5858</v>
+        <v>2835</v>
       </c>
       <c r="C2" t="n">
-        <v>4310</v>
+        <v>6029</v>
       </c>
       <c r="D2" t="n">
-        <v>27835</v>
+        <v>18276</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4068</v>
+        <v>2885</v>
       </c>
       <c r="C3" t="n">
-        <v>3856</v>
+        <v>8142</v>
       </c>
       <c r="D3" t="n">
-        <v>3764</v>
+        <v>5941</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1302</v>
+        <v>632</v>
       </c>
       <c r="C4" t="n">
-        <v>2206</v>
+        <v>2005</v>
       </c>
       <c r="D4" t="n">
-        <v>1635</v>
+        <v>1702</v>
       </c>
     </row>
     <row r="5">
@@ -4865,13 +4865,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>126</v>
+        <v>100</v>
       </c>
       <c r="C5" t="n">
-        <v>221</v>
+        <v>208</v>
       </c>
       <c r="D5" t="n">
-        <v>1186</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="6">
@@ -4879,13 +4879,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>185</v>
+        <v>137</v>
       </c>
       <c r="C6" t="n">
-        <v>410</v>
+        <v>340</v>
       </c>
       <c r="D6" t="n">
-        <v>870</v>
+        <v>747</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>158</v>
+        <v>113</v>
       </c>
       <c r="C7" t="n">
-        <v>409</v>
+        <v>324</v>
       </c>
       <c r="D7" t="n">
-        <v>584</v>
+        <v>509</v>
       </c>
     </row>
     <row r="8">
@@ -4907,13 +4907,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>115</v>
+        <v>83</v>
       </c>
       <c r="C8" t="n">
-        <v>307</v>
+        <v>244</v>
       </c>
       <c r="D8" t="n">
-        <v>439</v>
+        <v>395</v>
       </c>
     </row>
     <row r="9">
@@ -4921,13 +4921,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>84</v>
+        <v>64</v>
       </c>
       <c r="C9" t="n">
-        <v>232</v>
+        <v>188</v>
       </c>
       <c r="D9" t="n">
-        <v>363</v>
+        <v>319</v>
       </c>
     </row>
     <row r="10">
@@ -4935,13 +4935,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>63</v>
+        <v>47</v>
       </c>
       <c r="C10" t="n">
-        <v>190</v>
+        <v>161</v>
       </c>
       <c r="D10" t="n">
-        <v>352</v>
+        <v>318</v>
       </c>
     </row>
     <row r="11">
@@ -4949,13 +4949,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="C11" t="n">
-        <v>166</v>
+        <v>140</v>
       </c>
       <c r="D11" t="n">
-        <v>270</v>
+        <v>244</v>
       </c>
     </row>
     <row r="12">
@@ -4963,13 +4963,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C12" t="n">
-        <v>135</v>
+        <v>113</v>
       </c>
       <c r="D12" t="n">
-        <v>206</v>
+        <v>187</v>
       </c>
     </row>
     <row r="13">
@@ -4977,13 +4977,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="C13" t="n">
-        <v>103</v>
+        <v>88</v>
       </c>
       <c r="D13" t="n">
-        <v>172</v>
+        <v>155</v>
       </c>
     </row>
     <row r="14">
@@ -4991,13 +4991,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="D14" t="n">
-        <v>146</v>
+        <v>134</v>
       </c>
     </row>
     <row r="15">
@@ -5005,13 +5005,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C15" t="n">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="D15" t="n">
-        <v>120</v>
+        <v>112</v>
       </c>
     </row>
     <row r="16">
@@ -5019,13 +5019,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="D16" t="n">
-        <v>98</v>
+        <v>90</v>
       </c>
     </row>
     <row r="17">
@@ -5033,13 +5033,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C17" t="n">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="D17" t="n">
-        <v>78</v>
+        <v>74</v>
       </c>
     </row>
     <row r="18">
@@ -5047,13 +5047,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
     </row>
     <row r="19">
@@ -5061,13 +5061,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="D19" t="n">
-        <v>40</v>
+        <v>37</v>
       </c>
     </row>
     <row r="20">
@@ -5078,10 +5078,10 @@
         <v>9</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="21">
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C21" t="n">
-        <v>106</v>
+        <v>92</v>
       </c>
       <c r="D21" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5302</v>
+        <v>1765</v>
       </c>
       <c r="C2" t="n">
-        <v>2578</v>
+        <v>5584</v>
       </c>
       <c r="D2" t="n">
-        <v>27545</v>
+        <v>14959</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4063</v>
+        <v>2359</v>
       </c>
       <c r="C3" t="n">
-        <v>3552</v>
+        <v>5960</v>
       </c>
       <c r="D3" t="n">
-        <v>7344</v>
+        <v>7576</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2286</v>
+        <v>1547</v>
       </c>
       <c r="C4" t="n">
-        <v>3094</v>
+        <v>5616</v>
       </c>
       <c r="D4" t="n">
-        <v>1994</v>
+        <v>2504</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>584</v>
+        <v>317</v>
       </c>
       <c r="C5" t="n">
-        <v>1302</v>
+        <v>1238</v>
       </c>
       <c r="D5" t="n">
-        <v>1220</v>
+        <v>1131</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>149</v>
+        <v>112</v>
       </c>
       <c r="C6" t="n">
-        <v>305</v>
+        <v>262</v>
       </c>
       <c r="D6" t="n">
-        <v>915</v>
+        <v>794</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>158</v>
+        <v>115</v>
       </c>
       <c r="C7" t="n">
-        <v>405</v>
+        <v>332</v>
       </c>
       <c r="D7" t="n">
-        <v>628</v>
+        <v>548</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>125</v>
+        <v>90</v>
       </c>
       <c r="C8" t="n">
-        <v>358</v>
+        <v>286</v>
       </c>
       <c r="D8" t="n">
-        <v>454</v>
+        <v>407</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>90</v>
+        <v>67</v>
       </c>
       <c r="C9" t="n">
-        <v>268</v>
+        <v>216</v>
       </c>
       <c r="D9" t="n">
-        <v>371</v>
+        <v>329</v>
       </c>
     </row>
     <row r="10">
@@ -5246,13 +5246,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>67</v>
+        <v>50</v>
       </c>
       <c r="C10" t="n">
-        <v>209</v>
+        <v>174</v>
       </c>
       <c r="D10" t="n">
-        <v>346</v>
+        <v>314</v>
       </c>
     </row>
     <row r="11">
@@ -5260,13 +5260,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>47</v>
+        <v>36</v>
       </c>
       <c r="C11" t="n">
-        <v>175</v>
+        <v>149</v>
       </c>
       <c r="D11" t="n">
-        <v>280</v>
+        <v>253</v>
       </c>
     </row>
     <row r="12">
@@ -5274,13 +5274,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C12" t="n">
-        <v>148</v>
+        <v>125</v>
       </c>
       <c r="D12" t="n">
-        <v>213</v>
+        <v>191</v>
       </c>
     </row>
     <row r="13">
@@ -5288,13 +5288,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="C13" t="n">
-        <v>116</v>
+        <v>98</v>
       </c>
       <c r="D13" t="n">
-        <v>173</v>
+        <v>158</v>
       </c>
     </row>
     <row r="14">
@@ -5302,13 +5302,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="D14" t="n">
-        <v>148</v>
+        <v>135</v>
       </c>
     </row>
     <row r="15">
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C15" t="n">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="D15" t="n">
-        <v>120</v>
+        <v>112</v>
       </c>
     </row>
     <row r="16">
@@ -5330,13 +5330,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C16" t="n">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="D16" t="n">
-        <v>99</v>
+        <v>91</v>
       </c>
     </row>
     <row r="17">
@@ -5344,13 +5344,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C17" t="n">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="D17" t="n">
-        <v>79</v>
+        <v>75</v>
       </c>
     </row>
     <row r="18">
@@ -5358,13 +5358,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
     </row>
     <row r="19">
@@ -5372,13 +5372,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="20">
@@ -5389,10 +5389,10 @@
         <v>8</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="21">
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C21" t="n">
-        <v>122</v>
+        <v>106</v>
       </c>
       <c r="D21" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5143</v>
+        <v>2306</v>
       </c>
       <c r="C2" t="n">
-        <v>3335</v>
+        <v>5514</v>
       </c>
       <c r="D2" t="n">
-        <v>21744</v>
+        <v>17147</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3828</v>
+        <v>1716</v>
       </c>
       <c r="C3" t="n">
-        <v>2655</v>
+        <v>4981</v>
       </c>
       <c r="D3" t="n">
-        <v>9897</v>
+        <v>8211</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2698</v>
+        <v>1670</v>
       </c>
       <c r="C4" t="n">
-        <v>3275</v>
+        <v>5694</v>
       </c>
       <c r="D4" t="n">
-        <v>2909</v>
+        <v>3401</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1178</v>
+        <v>790</v>
       </c>
       <c r="C5" t="n">
-        <v>2191</v>
+        <v>3607</v>
       </c>
       <c r="D5" t="n">
-        <v>1304</v>
+        <v>1336</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>317</v>
+        <v>192</v>
       </c>
       <c r="C6" t="n">
-        <v>808</v>
+        <v>774</v>
       </c>
       <c r="D6" t="n">
-        <v>955</v>
+        <v>844</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>143</v>
+        <v>106</v>
       </c>
       <c r="C7" t="n">
-        <v>354</v>
+        <v>295</v>
       </c>
       <c r="D7" t="n">
-        <v>663</v>
+        <v>585</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>130</v>
+        <v>94</v>
       </c>
       <c r="C8" t="n">
-        <v>376</v>
+        <v>306</v>
       </c>
       <c r="D8" t="n">
-        <v>478</v>
+        <v>422</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>96</v>
+        <v>71</v>
       </c>
       <c r="C9" t="n">
-        <v>310</v>
+        <v>250</v>
       </c>
       <c r="D9" t="n">
-        <v>376</v>
+        <v>338</v>
       </c>
     </row>
     <row r="10">
@@ -5557,13 +5557,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>71</v>
+        <v>52</v>
       </c>
       <c r="C10" t="n">
-        <v>235</v>
+        <v>193</v>
       </c>
       <c r="D10" t="n">
-        <v>346</v>
+        <v>313</v>
       </c>
     </row>
     <row r="11">
@@ -5571,13 +5571,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="C11" t="n">
-        <v>187</v>
+        <v>160</v>
       </c>
       <c r="D11" t="n">
-        <v>286</v>
+        <v>256</v>
       </c>
     </row>
     <row r="12">
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="C12" t="n">
-        <v>159</v>
+        <v>135</v>
       </c>
       <c r="D12" t="n">
-        <v>217</v>
+        <v>198</v>
       </c>
     </row>
     <row r="13">
@@ -5599,13 +5599,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="C13" t="n">
-        <v>128</v>
+        <v>109</v>
       </c>
       <c r="D13" t="n">
-        <v>176</v>
+        <v>160</v>
       </c>
     </row>
     <row r="14">
@@ -5613,13 +5613,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>99</v>
+        <v>86</v>
       </c>
       <c r="D14" t="n">
-        <v>148</v>
+        <v>135</v>
       </c>
     </row>
     <row r="15">
@@ -5627,13 +5627,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C15" t="n">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="D15" t="n">
-        <v>122</v>
+        <v>113</v>
       </c>
     </row>
     <row r="16">
@@ -5641,13 +5641,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C16" t="n">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="D16" t="n">
-        <v>100</v>
+        <v>92</v>
       </c>
     </row>
     <row r="17">
@@ -5655,13 +5655,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C17" t="n">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="D17" t="n">
-        <v>79</v>
+        <v>75</v>
       </c>
     </row>
     <row r="18">
@@ -5669,13 +5669,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>60</v>
+        <v>56</v>
       </c>
     </row>
     <row r="19">
@@ -5683,13 +5683,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C19" t="n">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="20">
@@ -5700,10 +5700,10 @@
         <v>7</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="21">
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C21" t="n">
-        <v>137</v>
+        <v>119</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5624</v>
+        <v>2936</v>
       </c>
       <c r="C2" t="n">
-        <v>5056</v>
+        <v>11924</v>
       </c>
       <c r="D2" t="n">
-        <v>19851</v>
+        <v>20320</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3253</v>
+        <v>1656</v>
       </c>
       <c r="C3" t="n">
-        <v>2459</v>
+        <v>4574</v>
       </c>
       <c r="D3" t="n">
-        <v>10350</v>
+        <v>8991</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2013</v>
+        <v>1455</v>
       </c>
       <c r="C4" t="n">
-        <v>2377</v>
+        <v>5192</v>
       </c>
       <c r="D4" t="n">
-        <v>3551</v>
+        <v>4174</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1008</v>
+        <v>1056</v>
       </c>
       <c r="C5" t="n">
-        <v>2018</v>
+        <v>4613</v>
       </c>
       <c r="D5" t="n">
-        <v>1262</v>
+        <v>1639</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>357</v>
+        <v>416</v>
       </c>
       <c r="C6" t="n">
-        <v>1008</v>
+        <v>2179</v>
       </c>
       <c r="D6" t="n">
-        <v>772</v>
+        <v>917</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>99</v>
+        <v>133</v>
       </c>
       <c r="C7" t="n">
-        <v>371</v>
+        <v>526</v>
       </c>
       <c r="D7" t="n">
-        <v>516</v>
+        <v>622</v>
       </c>
     </row>
     <row r="8">
@@ -5840,13 +5840,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>58</v>
+        <v>92</v>
       </c>
       <c r="C8" t="n">
-        <v>223</v>
+        <v>300</v>
       </c>
       <c r="D8" t="n">
-        <v>360</v>
+        <v>439</v>
       </c>
     </row>
     <row r="9">
@@ -5854,13 +5854,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>44</v>
+        <v>75</v>
       </c>
       <c r="C9" t="n">
-        <v>197</v>
+        <v>275</v>
       </c>
       <c r="D9" t="n">
-        <v>268</v>
+        <v>347</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>31</v>
+        <v>55</v>
       </c>
       <c r="C10" t="n">
-        <v>152</v>
+        <v>218</v>
       </c>
       <c r="D10" t="n">
-        <v>237</v>
+        <v>310</v>
       </c>
     </row>
     <row r="11">
@@ -5882,13 +5882,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>21</v>
+        <v>39</v>
       </c>
       <c r="C11" t="n">
-        <v>113</v>
+        <v>173</v>
       </c>
       <c r="D11" t="n">
-        <v>194</v>
+        <v>261</v>
       </c>
     </row>
     <row r="12">
@@ -5896,13 +5896,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="C12" t="n">
-        <v>92</v>
+        <v>143</v>
       </c>
       <c r="D12" t="n">
-        <v>148</v>
+        <v>203</v>
       </c>
     </row>
     <row r="13">
@@ -5910,13 +5910,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="C13" t="n">
-        <v>74</v>
+        <v>119</v>
       </c>
       <c r="D13" t="n">
-        <v>116</v>
+        <v>161</v>
       </c>
     </row>
     <row r="14">
@@ -5924,13 +5924,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>57</v>
+        <v>94</v>
       </c>
       <c r="D14" t="n">
-        <v>97</v>
+        <v>136</v>
       </c>
     </row>
     <row r="15">
@@ -5938,13 +5938,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C15" t="n">
-        <v>45</v>
+        <v>76</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>114</v>
       </c>
     </row>
     <row r="16">
@@ -5952,13 +5952,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C16" t="n">
-        <v>38</v>
+        <v>67</v>
       </c>
       <c r="D16" t="n">
-        <v>63</v>
+        <v>92</v>
       </c>
     </row>
     <row r="17">
@@ -5966,13 +5966,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C17" t="n">
-        <v>35</v>
+        <v>62</v>
       </c>
       <c r="D17" t="n">
-        <v>50</v>
+        <v>76</v>
       </c>
     </row>
     <row r="18">
@@ -5980,13 +5980,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>56</v>
       </c>
     </row>
     <row r="19">
@@ -5994,13 +5994,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>40</v>
       </c>
     </row>
     <row r="20">
@@ -6008,13 +6008,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
     </row>
     <row r="21">
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>75</v>
+        <v>132</v>
       </c>
       <c r="D21" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4964</v>
+        <v>3434</v>
       </c>
       <c r="C2" t="n">
-        <v>8042</v>
+        <v>13621</v>
       </c>
       <c r="D2" t="n">
-        <v>14941</v>
+        <v>24683</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3704</v>
+        <v>1823</v>
       </c>
       <c r="C3" t="n">
-        <v>3438</v>
+        <v>7068</v>
       </c>
       <c r="D3" t="n">
-        <v>11243</v>
+        <v>10003</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2319</v>
+        <v>1339</v>
       </c>
       <c r="C4" t="n">
-        <v>2377</v>
+        <v>4725</v>
       </c>
       <c r="D4" t="n">
-        <v>4878</v>
+        <v>4879</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1357</v>
+        <v>1096</v>
       </c>
       <c r="C5" t="n">
-        <v>2189</v>
+        <v>4800</v>
       </c>
       <c r="D5" t="n">
-        <v>1685</v>
+        <v>1987</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="C6" t="n">
-        <v>1567</v>
+        <v>3301</v>
       </c>
       <c r="D6" t="n">
-        <v>847</v>
+        <v>1022</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>210</v>
+        <v>226</v>
       </c>
       <c r="C7" t="n">
-        <v>739</v>
+        <v>1282</v>
       </c>
       <c r="D7" t="n">
-        <v>560</v>
+        <v>661</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>72</v>
+        <v>101</v>
       </c>
       <c r="C8" t="n">
-        <v>305</v>
+        <v>401</v>
       </c>
       <c r="D8" t="n">
-        <v>385</v>
+        <v>457</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>46</v>
+        <v>75</v>
       </c>
       <c r="C9" t="n">
-        <v>210</v>
+        <v>285</v>
       </c>
       <c r="D9" t="n">
-        <v>278</v>
+        <v>356</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>34</v>
+        <v>58</v>
       </c>
       <c r="C10" t="n">
-        <v>175</v>
+        <v>241</v>
       </c>
       <c r="D10" t="n">
-        <v>240</v>
+        <v>308</v>
       </c>
     </row>
     <row r="11">
@@ -6193,13 +6193,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>23</v>
+        <v>41</v>
       </c>
       <c r="C11" t="n">
-        <v>132</v>
+        <v>188</v>
       </c>
       <c r="D11" t="n">
-        <v>199</v>
+        <v>265</v>
       </c>
     </row>
     <row r="12">
@@ -6207,13 +6207,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="C12" t="n">
-        <v>102</v>
+        <v>154</v>
       </c>
       <c r="D12" t="n">
-        <v>152</v>
+        <v>208</v>
       </c>
     </row>
     <row r="13">
@@ -6221,13 +6221,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="C13" t="n">
-        <v>82</v>
+        <v>127</v>
       </c>
       <c r="D13" t="n">
-        <v>119</v>
+        <v>162</v>
       </c>
     </row>
     <row r="14">
@@ -6235,13 +6235,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>64</v>
+        <v>101</v>
       </c>
       <c r="D14" t="n">
-        <v>98</v>
+        <v>137</v>
       </c>
     </row>
     <row r="15">
@@ -6249,13 +6249,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C15" t="n">
-        <v>50</v>
+        <v>81</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>114</v>
       </c>
     </row>
     <row r="16">
@@ -6263,13 +6263,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C16" t="n">
-        <v>40</v>
+        <v>69</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>93</v>
       </c>
     </row>
     <row r="17">
@@ -6277,13 +6277,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C17" t="n">
-        <v>36</v>
+        <v>63</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>76</v>
       </c>
     </row>
     <row r="18">
@@ -6291,13 +6291,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>56</v>
       </c>
     </row>
     <row r="19">
@@ -6305,13 +6305,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>41</v>
       </c>
     </row>
     <row r="20">
@@ -6319,13 +6319,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
     </row>
     <row r="21">
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>84</v>
+        <v>144</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6228</v>
+        <v>3042</v>
       </c>
       <c r="C2" t="n">
-        <v>7087</v>
+        <v>8499</v>
       </c>
       <c r="D2" t="n">
-        <v>18859</v>
+        <v>19543</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3563</v>
+        <v>2398</v>
       </c>
       <c r="C3" t="n">
-        <v>5180</v>
+        <v>10815</v>
       </c>
       <c r="D3" t="n">
-        <v>11025</v>
+        <v>11164</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2585</v>
+        <v>1012</v>
       </c>
       <c r="C4" t="n">
-        <v>2915</v>
+        <v>7511</v>
       </c>
       <c r="D4" t="n">
-        <v>5904</v>
+        <v>4660</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1632</v>
+        <v>585</v>
       </c>
       <c r="C5" t="n">
-        <v>2249</v>
+        <v>3234</v>
       </c>
       <c r="D5" t="n">
-        <v>2246</v>
+        <v>1573</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>905</v>
+        <v>208</v>
       </c>
       <c r="C6" t="n">
-        <v>1888</v>
+        <v>1256</v>
       </c>
       <c r="D6" t="n">
-        <v>979</v>
+        <v>647</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>377</v>
+        <v>93</v>
       </c>
       <c r="C7" t="n">
-        <v>1184</v>
+        <v>392</v>
       </c>
       <c r="D7" t="n">
-        <v>607</v>
+        <v>447</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>123</v>
+        <v>69</v>
       </c>
       <c r="C8" t="n">
-        <v>530</v>
+        <v>279</v>
       </c>
       <c r="D8" t="n">
-        <v>411</v>
+        <v>348</v>
       </c>
     </row>
     <row r="9">
@@ -6479,10 +6479,10 @@
         <v>53</v>
       </c>
       <c r="C9" t="n">
-        <v>255</v>
+        <v>236</v>
       </c>
       <c r="D9" t="n">
-        <v>290</v>
+        <v>301</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C10" t="n">
-        <v>192</v>
+        <v>184</v>
       </c>
       <c r="D10" t="n">
-        <v>243</v>
+        <v>259</v>
       </c>
     </row>
     <row r="11">
@@ -6504,13 +6504,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C11" t="n">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D11" t="n">
-        <v>201</v>
+        <v>203</v>
       </c>
     </row>
     <row r="12">
@@ -6518,13 +6518,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C12" t="n">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="D12" t="n">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="13">
@@ -6532,13 +6532,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="D13" t="n">
-        <v>122</v>
+        <v>134</v>
       </c>
     </row>
     <row r="14">
@@ -6546,13 +6546,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C14" t="n">
-        <v>70</v>
+        <v>79</v>
       </c>
       <c r="D14" t="n">
-        <v>98</v>
+        <v>111</v>
       </c>
     </row>
     <row r="15">
@@ -6560,13 +6560,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C15" t="n">
-        <v>55</v>
+        <v>67</v>
       </c>
       <c r="D15" t="n">
-        <v>80</v>
+        <v>91</v>
       </c>
     </row>
     <row r="16">
@@ -6574,13 +6574,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C16" t="n">
-        <v>43</v>
+        <v>61</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>74</v>
       </c>
     </row>
     <row r="17">
@@ -6588,13 +6588,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C17" t="n">
-        <v>37</v>
+        <v>57</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>54</v>
       </c>
     </row>
     <row r="18">
@@ -6602,13 +6602,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C18" t="n">
-        <v>34</v>
+        <v>54</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="19">
@@ -6616,13 +6616,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>52</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
     </row>
     <row r="20">
@@ -6630,13 +6630,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>144</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
     </row>
     <row r="21">
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>92</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
